--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -538,11 +538,11 @@
         <v>262</v>
       </c>
       <c r="H2" t="n">
-        <v>627034561238</v>
+        <v>627374007311</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35.491</t>
+          <t>35.510</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://open.api.nexon.com/static/maplestorytw/character/look/CAJBOILNCNBLOGHECFAMIKNBDCHDEFGILBCFHMPODJNOHDJPHPGJLIDPHKPEKGIBOGDILGJMABKAMALJLDCDELPAAEIEOIBALFIDJKOKIGFMFEJPLGHEHAIBPHCDOPHNHDBACCLNMILNAMIPAADIHFPOOPGEGNLENEOLCHMJGHJJKPJKPOHKHJPFIBHAICDDIKIPPKNDHNMHBMJKFOGDOIJLJGBHLODLFKPDHJLKMIMCDMAMCBLGBDIJLHFDGPANLOOJPHOAKDPOACLNMEIMJGLCIJJMCALDMLELKDDJINLJJJMOIICPCFAMEOLPJCNJCHBFJAKBDMBJJJMOPFCGPJFIHGMFPGFNBMJBKCIPPPDADNLAJHFGBBDIHCOMJGAIIFFGLEGFLMCIJIFEAMJAMOAJPJFGEKLJLADGOEKEEPFKMEMBPNJBMIAPKJGPLHFHAPNMIHEMOLAOEBIDBKGBJCCKDFIMEKBABIACLFAMFJJJENEOIDLBLBDDIMJCIPDNILHFAJDFEHEPDEPPLABJDKMLAGKBIPCCHGKCAANCAPNHMGNLAPBEBLJDDCMBGODHBMFHOJNNDDKHAMFBDKOHAPPFJGPFECGMDFPACIEPNMHDJHMDFDOAKHGLJNPJEBIMDIAIADDAIJKNEPJMBCHAOGDALLFODGOIEGLOOPCAJGDJFFELFGOPGHNFFGEAJMBFLFDDEJOIMDMINDDHONFOJIMCNALGEPNKJMICGLCJHMJCDMAGAKMHMGPIFBKHCKGEOJOALLFAADHEGENLGOFFJNNGLACDCBKNGBFCBCIMJOBOBINHIGFKEMKNLJMJLODJMMOACOGINPDJCONJPIODJBHELKGGPJAHKDBCILCLAOJMOFJIDOGDOOCHIKOGALJOHKEILAHMDFAJJAALNHLOIDDMDABLJNCIKHIKJLBHBINJMMKNMELFLOFGHHBEIDGLLKFDHBBILDEMAFCHJNAGPMLLAMOODLKLMLJADOGLJPDBLAGIDEFFBAADICDEHAKO</t>
+          <t>https://open.api.nexon.com/static/maplestorytw/character/look/GOOKFPNPPDDJCHJGMPEPBIPALMFDFJMGGCPGLBGBPNBFEBJJNNOPOOFHGBOEMBCKHOHOCFECJPCDNPDGNLMNFCLLJOHEGDHLKGBNFCEBIMOJMNONOHHMFHJKAEOOCJEJNECKPKCDLLECBJMFCCHPBKHOELGHNKCMGINLLPHEAFLHAJJBFDECMHAIDDPJDNDMLCJMADMHDCNKJDBKCDAMDGPMLGELCKACPKLMIDELDNPCKMKMNLLDJNKHJANKDACOOCBGAHJHCABHANIFGJGCEAAFKFEJONKGDFHIBGJIMBLOPNCBFOCHNPNHLDIKJBDBEMODOLILJGLJPFLOPJJFDMPFEIHHKNHJMFDCBEKNKJHMNLHBMPHLLCBGMOLIHINFFMFPCPFCJCCGNIJBBCKHEMDFBODGPMFEADNLLLHGFHAGAKFIMBKBHILBONLANHILBPKOEHHCOBNEHOHJFNECIEAEGILBENKGBKKKNCFMJKDBHNDAOJHENPPCNNOHGDEPOCOFIBAINKPLHICLDKBEMOIINKHMGLIJMEABALJCFHIEMPFHMNGIKAHJJIDHPCMOFDMHOPJCGMFHKPJGBBHGPELBCJHKKBFCCNIPGLDPCIFFKEJMPKMKJCFNPLPGAEFNFDOBJCHEOIACCFJLHHLOCJIICIDMGNOOOIAEIJEDOGDFLNFNEAMEKIMIFKKIKJDOBFEEFILKPMFAKCMJHBCGBIILAGHPEFFJIJJLAJKJNBBJIEDNCFHAIFOCMJFJCMDPGEPGFIOFKFMJMEBCOOALNMLHLGAGPGCBJLDGGJPEMMFLJHOPIFGLOICJPLCJKDGFMDLBFHEJHNILAIKJEDHNFLGIIAHFJPIEMDKJCODIOPEJAEELHLHENPLKGCDONOMOEOHFPFOKEBOKGFFKLDCJOMGDFALDLJFHGDEIIFAABLONLKEKAGNBBHFMIMGMPLIMKDHEGDNMACECOCNCDNNOPAFPAFPDMGLGJDDPALNBHJGMLKDLPCOPMLPCHEGGLGHP</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '8799473'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '9777191'}, {'stat_name': '傷害', 'stat_value': '108.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '425.50'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '95.92'}, {'stat_name': '爆擊機率', 'stat_value': '107'}, {'stat_name': '爆擊傷害', 'stat_value': '88.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44700'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '70'}, {'stat_name': 'STR', 'stat_value': '23974'}, {'stat_name': 'DEX', 'stat_value': '2562'}, {'stat_name': 'INT', 'stat_value': '1482'}, {'stat_name': 'LUK', 'stat_value': '1322'}, {'stat_name': 'HP', 'stat_value': '71053'}, {'stat_name': 'MP', 'stat_value': '23041'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '70'}, {'stat_name': '攻擊速度', 'stat_value': '6'}, {'stat_name': '一般怪物傷害', 'stat_value': '32.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '45.00'}, {'stat_name': '攻擊力', 'stat_value': '2195'}, {'stat_name': '魔法攻擊力', 'stat_value': '632'}, {'stat_name': '戰鬥力', 'stat_value': '16059346'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
+          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '8801375'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '9779303'}, {'stat_name': '傷害', 'stat_value': '108.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '435.50'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '95.92'}, {'stat_name': '爆擊機率', 'stat_value': '91'}, {'stat_name': '爆擊傷害', 'stat_value': '83.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44069'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '70'}, {'stat_name': 'STR', 'stat_value': '23536'}, {'stat_name': 'DEX', 'stat_value': '2400'}, {'stat_name': 'INT', 'stat_value': '1952'}, {'stat_name': 'LUK', 'stat_value': '1903'}, {'stat_name': 'HP', 'stat_value': '70905'}, {'stat_name': 'MP', 'stat_value': '25077'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '86'}, {'stat_name': '攻擊速度', 'stat_value': '6'}, {'stat_name': '一般怪物傷害', 'stat_value': '32.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '37.50'}, {'stat_name': '攻擊力', 'stat_value': '2239'}, {'stat_name': '魔法攻擊力', 'stat_value': '704'}, {'stat_name': '戰鬥力', 'stat_value': '16420080'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -755,7 +755,7 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>523980</v>
+        <v>535830</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\\r\\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\\r\\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\\r\\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\\r\\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\\r\\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\\r\\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\\r\\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\\r\\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\\r\\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\\n套用主武器的攻擊力和魔力中較高的值\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\\r\\n實體化在楓之谷成就選擇的徽章。\\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯I', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯跳躍並發射衝擊波攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯跳躍：對最多10名敵人造成500%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKA', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯II', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯啃咬前方，攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯撕咬：對最多10名敵人造成550%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 2, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKB', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯III', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯以鋒利的爪子攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯利爪：對最多10名敵人造成600%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKC', 'skill_effect_next': None}, {'skill_name': '幻影魔法', 'skill_description': '[等級上限 : 1]\\r\\n由記憶與回憶的幻影交織而成的神祕魔法。', 'skill_level': 1, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKF', 'skill_effect_next': None}, {'skill_name': '利爪的艾拉諾斯II', 'skill_description': '[最高等級：1]\\n每當消滅等級範圍怪物時可累積計量表，\\n當計量表全滿時，即可發動&lt;利爪的艾拉諾斯II&gt;。\\n\\n每日&lt;利爪的艾拉諾斯II&gt;發動次數達到20次時\\n結束。\\n\\n活動期間結束後將無法使用。\\n\\n - 變更開關\\n右擊新手技能欄&lt;利爪的艾拉諾斯II&gt;技能\\n - 變更自動/手動\\n右擊UI的&lt;利爪的艾拉諾斯II&gt;技能\\n', 'skill_level': 1, 'skill_effect': '\\n\\n&lt;利爪的艾拉諾斯II&gt;最多對15名敵人以3000%傷害攻擊1次的\\n爆炸發動6次的技能發動6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEB', 'skill_effect_next': None}, {'skill_name': '古代力量', 'skill_description': '[等級上限 : 1]\\r\\n隨著透過調查逐步找回力量，將會越來越強。', 'skill_level': 1, 'skill_effect': '攻擊力/魔力增加 15\r\n攻擊BOSS怪物時傷害增加40%\r\n無視怪物防禦率增加40%\r\n攻擊一般怪物時傷害增加 20%\r\n經驗值獲得量增加10.0%\r\n消滅BOSS怪物時獲得的靈魂艾爾達氣息增加80%\r\n從怪物公園退場時獲得的經驗值增加50%\r\n完成奧術之河每日任務時，獲得經驗值增加50%、獲得符文增加20個\r\n真實之力增加40\r\n從怪物公園退場時獲得的經驗值增加30%\r\n智慧餘響經驗值增加200%\r\n消滅BOSS怪物時，獲得的靈魂艾爾達氣息增加40%\r\n完成奧術之河每日任務時，增加20%獲得的經驗值、4個獲得的符文\r\n完成格蘭蒂斯每日任務時，增加20%獲得的經驗值、3個獲得的符文\r\n狩獵場獲得靈魂艾爾達氣息100%增加\r\n攻擊BOSS怪物時傷害增加10%\r\n史詩副本基本經驗值獎勵獲得量100%增加', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEH', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\\r\\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\\r\\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\\r\\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\\r\\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\\r\\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\\r\\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\\r\\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\\r\\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\\r\\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\\n套用主武器的攻擊力和魔力中較高的值\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\\r\\n實體化在楓之谷成就選擇的徽章。\\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯I', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯跳躍並發射衝擊波攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯跳躍：對最多10名敵人造成500%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKA', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯II', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯啃咬前方，攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯撕咬：對最多10名敵人造成550%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 2, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKB', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯III', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯以鋒利的爪子攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯利爪：對最多10名敵人造成600%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKC', 'skill_effect_next': None}, {'skill_name': '幻影魔法', 'skill_description': '[等級上限 : 1]\\r\\n由記憶與回憶的幻影交織而成的神祕魔法。', 'skill_level': 1, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKF', 'skill_effect_next': None}, {'skill_name': '利爪的艾拉諾斯II', 'skill_description': '[最高等級：1]\\n每當消滅等級範圍怪物時可累積計量表，\\n當計量表全滿時，即可發動&lt;利爪的艾拉諾斯II&gt;。\\n\\n每日&lt;利爪的艾拉諾斯II&gt;發動次數達到20次時\\n結束。\\n\\n活動期間結束後將無法使用。\\n\\n - 變更開關\\n右擊新手技能欄&lt;利爪的艾拉諾斯II&gt;技能\\n - 變更自動/手動\\n右擊UI的&lt;利爪的艾拉諾斯II&gt;技能\\n', 'skill_level': 1, 'skill_effect': '\\n\\n&lt;利爪的艾拉諾斯II&gt;最多對15名敵人以3000%傷害攻擊1次的\\n爆炸發動6次的技能發動6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEB', 'skill_effect_next': None}, {'skill_name': '古代力量', 'skill_description': '[等級上限 : 1]\\r\\n隨著透過調查逐步找回力量，將會越來越強。', 'skill_level': 1, 'skill_effect': '攻擊力/魔力增加 15\r\n攻擊BOSS怪物時傷害增加40%\r\n無視怪物防禦率增加40%\r\n攻擊一般怪物時傷害增加 20%\r\n經驗值獲得量增加12.5%\r\n消滅BOSS怪物時獲得的靈魂艾爾達氣息增加100%\r\n從怪物公園退場時獲得的經驗值增加50%\r\n完成奧術之河每日任務時，獲得經驗值增加50%、獲得符文增加20個\r\n完成格蘭蒂斯每日任務時，增加30%獲得的經驗值、5個獲得的符文\r\n真實之力增加40\r\n從怪物公園退場時獲得的經驗值增加30%\r\n智慧餘響經驗值增加200%\r\n消滅BOSS怪物時，獲得的靈魂艾爾達氣息增加40%\r\n完成奧術之河每日任務時，增加20%獲得的經驗值、4個獲得的符文\r\n完成格蘭蒂斯每日任務時，增加20%獲得的經驗值、3個獲得的符文\r\n狩獵場獲得靈魂艾爾達氣息100%增加\r\n寶藏獵人經驗值獲得量100%增加\r\n攻擊BOSS怪物時傷害增加10%\r\n史詩副本基本經驗值獎勵獲得量100%增加', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEH', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1487,22 +1487,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '鷹眼戰士盔甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJFLF', 'item_description': None, 'item_shape_name': '鷹眼戰士盔甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJFLF', 'item_gender': None, 'item_total_option': {'str': '140', 'dex': '67', 'int': '0', 'luk': '0', 'max_hp': '1070', 'max_mp': '450', 'attack_power': '4', 'magic_power': '0', 'armor': '569', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '30', 'dex': '30', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '210', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'MaxHP +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '450', 'attack_power': '1', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '7', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '49', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '840', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '70', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '289', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '黃蜘蛛戰士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJGIE', 'item_description': None, 'item_shape_name': '黃蜘蛛戰士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJGIE', 'item_gender': None, 'item_total_option': {'str': '133', 'dex': '67', 'int': '8', 'luk': '0', 'max_hp': '950', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '545', 'speed': '0', 'jump': '1', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '30', 'dex': '30', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '210', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '0', 'int': '8', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '1', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '275', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '防禦力 +2%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_power': '20', 'magic_power': '20', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', '</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 20% 傷害', 'potential_option_2': '防禦力 +240', 'potential_option_3': 'LUK +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'MaxMP +3%', 'additional_potential_option_2': '移動速度 +4', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'DEX +3%', 'additional_potential_option_2': 'INT +6', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '鷹眼戰士盔甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJFLF', 'item_description': None, 'item_shape_name': '鷹眼戰士盔甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJFLF', 'item_gender': None, 'item_total_option': {'str': '140', 'dex': '67', 'int': '0', 'luk': '0', 'max_hp': '1070', 'max_mp': '450', 'attack_power': '4', 'magic_power': '0', 'armor': '569', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '30', 'dex': '30', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '210', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'MaxHP +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '450', 'attack_power': '1', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '7', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '49', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '840', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '70', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '289', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '黃蜘蛛戰士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJGIE', 'item_description': None, 'item_shape_name': '黃蜘蛛戰士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJGIE', 'item_gender': None, 'item_total_option': {'str': '133', 'dex': '67', 'int': '8', 'luk': '0', 'max_hp': '950', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '545', 'speed': '0', 'jump': '1', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '30', 'dex': '30', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '210', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '0', 'int': '8', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '1', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '275', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '防禦力 +2%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_power': '20', 'magic_power': '20', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', '</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 20% 傷害', 'potential_option_2': '防禦力 +240', 'potential_option_3': 'LUK +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'MaxMP +3%', 'additional_potential_option_2': '移動速度 +4', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'DEX +3%', 'additional_potential_option_2': 'INT +6', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '戒指', 'item_equipment_slot': '戒指4', 'item_name': '銀花戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_description': None, 'item_shape_name': '銀花戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_gender': None, 'item_total_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 110}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +12', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '3', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '鷹眼戰士盔甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJFLF', 'item_description': None, 'item_shape_name': '鷹眼戰士盔甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJFLF', 'item_gender': None, 'item_total_option': {'str': '140', 'dex': '67', 'int': '0', 'luk': '0', 'max_hp': '1070', 'max_mp': '450', 'attack_power': '4', 'magic_power': '0', 'armor': '569', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '30', 'dex': '30', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '210', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'MaxHP +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '450', 'attack_power': '1', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '7', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '49', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '840', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '70', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '289', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '黃蜘蛛戰士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJGIE', 'item_description': None, 'item_shape_name': '黃蜘蛛戰士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJGIE', 'item_gender': None, 'item_total_option': {'str': '133', 'dex': '67', 'int': '8', 'luk': '0', 'max_hp': '950', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '545', 'speed': '0', 'jump': '1', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '30', 'dex': '30', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '210', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '0', 'int': '8', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '1', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '275', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_r</t>
+          <t>[{'item_equipment_part': '戒指', 'item_equipment_slot': '戒指4', 'item_name': '銀花戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_description': None, 'item_shape_name': '銀花戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_gender': None, 'item_total_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 110}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +12', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '3', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 20% 傷害', 'potential_option_2': '防禦力 +240', 'potential_option_3': 'LUK +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'MaxMP +3%', 'additional_potential_option_2': '移動速度 +4', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'DEX +3%', 'additional_potential_option_2': 'INT +6', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ig</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '鷹眼戰士盔甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJFLF', 'item_description': None, 'item_shape_name': '鷹眼戰士盔甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJFLF', 'item_gender': None, 'item_total_option': {'str': '140', 'dex': '67', 'int': '0', 'luk': '0', 'max_hp': '1070', 'max_mp': '450', 'attack_power': '4', 'magic_power': '0', 'armor': '569', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '30', 'dex': '30', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '210', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'MaxHP +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '450', 'attack_power': '1', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '7', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '49', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '840', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '70', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '289', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '黃蜘蛛戰士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJGIE', 'item_description': None, 'item_shape_name': '黃蜘蛛戰士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJGIE', 'item_gender': None, 'item_total_option': {'str': '133', 'dex': '67', 'int': '8', 'luk': '0', 'max_hp': '950', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '545', 'speed': '0', 'jump': '1', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '30', 'dex': '30', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '210', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '0', 'int': '8', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '1', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '275', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '防禦力 +2%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_power': '20', 'magic_power': '20', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', '</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 20% 傷害', 'potential_option_2': '防禦力 +240', 'potential_option_3': 'LUK +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'MaxMP +3%', 'additional_potential_option_2': '移動速度 +4', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'DEX +3%', 'additional_potential_option_2': 'INT +6', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -538,11 +538,11 @@
         <v>262</v>
       </c>
       <c r="H2" t="n">
-        <v>627374007311</v>
+        <v>627713453384</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35.510</t>
+          <t>35.530</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '8801375'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '9779303'}, {'stat_name': '傷害', 'stat_value': '108.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '435.50'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '95.92'}, {'stat_name': '爆擊機率', 'stat_value': '91'}, {'stat_name': '爆擊傷害', 'stat_value': '83.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44069'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '70'}, {'stat_name': 'STR', 'stat_value': '23536'}, {'stat_name': 'DEX', 'stat_value': '2400'}, {'stat_name': 'INT', 'stat_value': '1952'}, {'stat_name': 'LUK', 'stat_value': '1903'}, {'stat_name': 'HP', 'stat_value': '70905'}, {'stat_name': 'MP', 'stat_value': '25077'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '86'}, {'stat_name': '攻擊速度', 'stat_value': '6'}, {'stat_name': '一般怪物傷害', 'stat_value': '32.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '37.50'}, {'stat_name': '攻擊力', 'stat_value': '2239'}, {'stat_name': '魔法攻擊力', 'stat_value': '704'}, {'stat_name': '戰鬥力', 'stat_value': '16420080'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
+          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '11132337'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '12369262'}, {'stat_name': '傷害', 'stat_value': '138.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '437.00'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '96.02'}, {'stat_name': '爆擊機率', 'stat_value': '109'}, {'stat_name': '爆擊傷害', 'stat_value': '118.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '45341'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '70'}, {'stat_name': 'STR', 'stat_value': '24492'}, {'stat_name': 'DEX', 'stat_value': '2811'}, {'stat_name': 'INT', 'stat_value': '1465'}, {'stat_name': 'LUK', 'stat_value': '1687'}, {'stat_name': 'HP', 'stat_value': '70905'}, {'stat_name': 'MP', 'stat_value': '24528'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '90'}, {'stat_name': '攻擊速度', 'stat_value': '6'}, {'stat_name': '一般怪物傷害', 'stat_value': '32.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '47.50'}, {'stat_name': '攻擊力', 'stat_value': '2371'}, {'stat_name': '魔法攻擊力', 'stat_value': '743'}, {'stat_name': '戰鬥力', 'stat_value': '17791460'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>535830</v>
+        <v>547530</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\\r\\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\\r\\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\\r\\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\\r\\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\\r\\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\\r\\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\\r\\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\\r\\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\\r\\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\\n套用主武器的攻擊力和魔力中較高的值\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\\r\\n實體化在楓之谷成就選擇的徽章。\\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯I', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯跳躍並發射衝擊波攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯跳躍：對最多10名敵人造成500%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKA', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯II', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯啃咬前方，攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯撕咬：對最多10名敵人造成550%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 2, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKB', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯III', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯以鋒利的爪子攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯利爪：對最多10名敵人造成600%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKC', 'skill_effect_next': None}, {'skill_name': '幻影魔法', 'skill_description': '[等級上限 : 1]\\r\\n由記憶與回憶的幻影交織而成的神祕魔法。', 'skill_level': 1, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKF', 'skill_effect_next': None}, {'skill_name': '利爪的艾拉諾斯II', 'skill_description': '[最高等級：1]\\n每當消滅等級範圍怪物時可累積計量表，\\n當計量表全滿時，即可發動&lt;利爪的艾拉諾斯II&gt;。\\n\\n每日&lt;利爪的艾拉諾斯II&gt;發動次數達到20次時\\n結束。\\n\\n活動期間結束後將無法使用。\\n\\n - 變更開關\\n右擊新手技能欄&lt;利爪的艾拉諾斯II&gt;技能\\n - 變更自動/手動\\n右擊UI的&lt;利爪的艾拉諾斯II&gt;技能\\n', 'skill_level': 1, 'skill_effect': '\\n\\n&lt;利爪的艾拉諾斯II&gt;最多對15名敵人以3000%傷害攻擊1次的\\n爆炸發動6次的技能發動6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEB', 'skill_effect_next': None}, {'skill_name': '古代力量', 'skill_description': '[等級上限 : 1]\\r\\n隨著透過調查逐步找回力量，將會越來越強。', 'skill_level': 1, 'skill_effect': '攻擊力/魔力增加 15\r\n攻擊BOSS怪物時傷害增加40%\r\n無視怪物防禦率增加40%\r\n攻擊一般怪物時傷害增加 20%\r\n經驗值獲得量增加12.5%\r\n消滅BOSS怪物時獲得的靈魂艾爾達氣息增加100%\r\n從怪物公園退場時獲得的經驗值增加50%\r\n完成奧術之河每日任務時，獲得經驗值增加50%、獲得符文增加20個\r\n完成格蘭蒂斯每日任務時，增加30%獲得的經驗值、5個獲得的符文\r\n真實之力增加40\r\n從怪物公園退場時獲得的經驗值增加30%\r\n智慧餘響經驗值增加200%\r\n消滅BOSS怪物時，獲得的靈魂艾爾達氣息增加40%\r\n完成奧術之河每日任務時，增加20%獲得的經驗值、4個獲得的符文\r\n完成格蘭蒂斯每日任務時，增加20%獲得的經驗值、3個獲得的符文\r\n狩獵場獲得靈魂艾爾達氣息100%增加\r\n寶藏獵人經驗值獲得量100%增加\r\n攻擊BOSS怪物時傷害增加10%\r\n史詩副本基本經驗值獎勵獲得量100%增加', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEH', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\\r\\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\\r\\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\\r\\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\\r\\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\\r\\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\\r\\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\\r\\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\\r\\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\\r\\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\\n套用主武器的攻擊力和魔力中較高的值\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\\r\\n實體化在楓之谷成就選擇的徽章。\\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯I', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯跳躍並發射衝擊波攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯跳躍：對最多10名敵人造成500%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 4, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKA', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯II', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯啃咬前方，攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯撕咬：對最多10名敵人造成550%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 2, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKB', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯III', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯以鋒利的爪子攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯利爪：對最多10名敵人造成600%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKC', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯IV', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯猛烈咆哮，攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯咆哮：對最多10名敵人造成650%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 4, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKD', 'skill_effect_next': None}, {'skill_name': '幻影魔法', 'skill_description': '[等級上限 : 1]\\r\\n由記憶與回憶的幻影交織而成的神祕魔法。', 'skill_level': 1, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKF', 'skill_effect_next': None}, {'skill_name': '咆哮的艾拉諾斯', 'skill_description': '[最高等級：1]\\n每當消滅等級範圍怪物時可累積計量表，\\n當計量表全滿時，即可發動&lt;咆哮的艾拉諾斯&gt;。\\n\\n每日&lt;咆哮的艾拉諾斯&gt;發動次數達到20次時\\n結束。\\n\\n活動期間結束後將無法使用。\\n\\n - 變更開關\\n右擊新手技能欄&lt;咆哮的艾拉諾斯&gt;技能\\n - 變更自動/手動\\n右擊UI的&lt;咆哮的艾拉諾斯&gt;技能\\n', 'skill_level': 1, 'skill_effect': '\\n\\n&lt;咆哮的艾拉諾斯II&gt;最多對15名敵人以3000%傷害攻擊1次的\\n爆炸發動6次的技能發動6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEE', 'skill_effect_next': None}, {'skill_name': '古代力量', 'skill_description': '[等級上限 : 1]\\r\\n隨著透過調查逐步找回力量，將會越來越強。', 'skill_level': 1, 'skill_effect': '攻擊力/魔力增加 30\r\n攻擊BOSS怪物時傷害增加40%\r\n無視怪物防禦率增加40%\r\nBuff持續時間增加20%\r\n攻擊一般怪物時傷害增加 20%\r\n經驗值獲得量增加12.5%\r\n消滅BOSS怪物時獲得的靈魂艾爾達氣息增加100%\r\n從怪物公園退場時獲得的經驗值增加50%\r\n完成奧術之河每日任務時，獲得經驗值增加50%、獲得符文增加20個\r\n完成格蘭蒂斯每日任務時，增加50%獲得的經驗值、9個獲得的符文\r\n真實之力增加40\r\n從怪物公園退場時獲得的經驗值增加30%\r\n智慧餘響經驗值增加200%\r\n消滅BOSS怪物時，獲得的靈魂艾爾達氣息增加40%\r\n完成奧術之河每日任務時，增加20%獲得的經驗值、4個獲得的符文\r\n完成格蘭蒂斯每日任務時，增加20%獲得的經驗值、3個獲得的符文\r\n狩獵場獲得靈魂艾爾達氣息100%增加\r\n寶藏獵人經驗值獲得量100%增加\r\n攻擊BOSS怪物時傷害增加10%\r\n史詩副本基本經驗值獎勵獲得量150%增加', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEH', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1487,22 +1487,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 20% 傷害', 'potential_option_2': '防禦力 +240', 'potential_option_3': 'LUK +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'MaxMP +3%', 'additional_potential_option_2': '移動速度 +4', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'DEX +3%', 'additional_potential_option_2': 'INT +6', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊時有4%機率在7秒間無敵', 'potential_option_2': 'DEX +10%', 'potential_option_3': 'STR +16', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 20% 傷害', 'potential_option_2': '防禦力 +240', 'potential_option_3': 'LUK +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'MaxMP +3%', 'additional_potential_option_2': '移動速度 +4', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'DEX +3%', 'additional_potential_option_2': 'INT +6', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊時有4%機率在7秒間無敵', 'potential_option_2': 'DEX +10%', 'potential_option_3': 'STR +16', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '戒指', 'item_equipment_slot': '戒指4', 'item_name': '銀花戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_description': None, 'item_shape_name': '銀花戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_gender': None, 'item_total_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 110}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +12', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '3', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 20% 傷害', 'potential_option_2': '防禦力 +240', 'potential_option_3': 'LUK +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'MaxMP +3%', 'additional_potential_option_2': '移動速度 +4', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'DEX +3%', 'additional_potential_option_2': 'INT +6', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ig</t>
+          <t>[{'item_equipment_part': '戒指', 'item_equipment_slot': '戒指4', 'item_name': '銀花戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_description': None, 'item_shape_name': '銀花戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_gender': None, 'item_total_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 110}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +12', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '3', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊時有4%機率在7秒間無敵', 'potential_option_2': 'DEX +10%', 'potential_option_3': 'STR +16', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ig</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 20% 傷害', 'potential_option_2': '防禦力 +240', 'potential_option_3': 'LUK +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'MaxMP +3%', 'additional_potential_option_2': '移動速度 +4', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'DEX +3%', 'additional_potential_option_2': 'INT +6', 'additional_potential_option_3': '移動速度 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +3%', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊時有4%機率在7秒間無敵', 'potential_option_2': 'DEX +10%', 'potential_option_3': 'STR +16', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -538,11 +538,11 @@
         <v>262</v>
       </c>
       <c r="H2" t="n">
-        <v>627713453384</v>
+        <v>628043617747</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35.530</t>
+          <t>35.548</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '11132337'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '12369262'}, {'stat_name': '傷害', 'stat_value': '138.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '437.00'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '96.02'}, {'stat_name': '爆擊機率', 'stat_value': '109'}, {'stat_name': '爆擊傷害', 'stat_value': '118.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '45341'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '70'}, {'stat_name': 'STR', 'stat_value': '24492'}, {'stat_name': 'DEX', 'stat_value': '2811'}, {'stat_name': 'INT', 'stat_value': '1465'}, {'stat_name': 'LUK', 'stat_value': '1687'}, {'stat_name': 'HP', 'stat_value': '70905'}, {'stat_name': 'MP', 'stat_value': '24528'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '90'}, {'stat_name': '攻擊速度', 'stat_value': '6'}, {'stat_name': '一般怪物傷害', 'stat_value': '32.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '47.50'}, {'stat_name': '攻擊力', 'stat_value': '2371'}, {'stat_name': '魔法攻擊力', 'stat_value': '743'}, {'stat_name': '戰鬥力', 'stat_value': '17791460'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
+          <t>[{'stat_name': '最低屬性攻擊力', 'stat_value': '11894668'}, {'stat_name': '最高屬性攻擊力', 'stat_value': '13216296'}, {'stat_name': '傷害', 'stat_value': '138.00'}, {'stat_name': 'BOSS怪物傷害', 'stat_value': '437.00'}, {'stat_name': '最終傷害', 'stat_value': '67.31'}, {'stat_name': '無視防禦率', 'stat_value': '96.04'}, {'stat_name': '爆擊機率', 'stat_value': '109'}, {'stat_name': '爆擊傷害', 'stat_value': '118.00'}, {'stat_name': '狀態異常耐性', 'stat_value': '41'}, {'stat_name': '格擋', 'stat_value': '100'}, {'stat_name': '防禦力', 'stat_value': '44804'}, {'stat_name': '移動速度', 'stat_value': '170'}, {'stat_name': '跳躍力', 'stat_value': '123'}, {'stat_name': '星力', 'stat_value': '218'}, {'stat_name': '神秘力量', 'stat_value': '1350'}, {'stat_name': '真實之力', 'stat_value': '70'}, {'stat_name': 'STR', 'stat_value': '24241'}, {'stat_name': 'DEX', 'stat_value': '2572'}, {'stat_name': 'INT', 'stat_value': '1491'}, {'stat_name': 'LUK', 'stat_value': '1526'}, {'stat_name': 'HP', 'stat_value': '71409'}, {'stat_name': 'MP', 'stat_value': '24528'}, {'stat_name': 'AP配點STR', 'stat_value': '1328'}, {'stat_name': 'AP配點DEX', 'stat_value': '4'}, {'stat_name': 'AP配點INT', 'stat_value': '4'}, {'stat_name': 'AP配點LUK', 'stat_value': '4'}, {'stat_name': 'AP配點HP', 'stat_value': '0'}, {'stat_name': 'AP配點MP', 'stat_value': '0'}, {'stat_name': '道具掉落率', 'stat_value': '32'}, {'stat_name': '楓幣獲得量', 'stat_value': '16'}, {'stat_name': 'Buff持續時間', 'stat_value': '90'}, {'stat_name': '攻擊速度', 'stat_value': '6'}, {'stat_name': '一般怪物傷害', 'stat_value': '32.00'}, {'stat_name': '冷卻時間減少(秒)', 'stat_value': '0'}, {'stat_name': '冷卻時間減少(％)', 'stat_value': '5'}, {'stat_name': '未套用冷卻時間', 'stat_value': '3'}, {'stat_name': '無視屬性耐性', 'stat_value': '0.00'}, {'stat_name': '狀態異常追加傷害', 'stat_value': '11.00'}, {'stat_name': '武器熟練度', 'stat_value': '90'}, {'stat_name': '獲得額外經驗值', 'stat_value': '47.50'}, {'stat_name': '攻擊力', 'stat_value': '2565'}, {'stat_name': '魔法攻擊力', 'stat_value': '743'}, {'stat_name': '戰鬥力', 'stat_value': '19178232'}, {'stat_name': '召喚獸持續時間增加', 'stat_value': '12'}]</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -755,7 +755,7 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>547530</v>
+        <v>559380</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -1487,22 +1487,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊時有4%機率在7秒間無敵', 'potential_option_2': 'DEX +10%', 'potential_option_3': 'STR +16', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'MaxHP +300', 'potential_option_2': '被打擊後無敵時間 +2秒', 'potential_option_3': '被擊中時有5% 機率無視 20% 傷害', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000'</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊時有4%機率在7秒間無敵', 'potential_option_2': 'DEX +10%', 'potential_option_3': 'STR +16', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'MaxHP +300', 'potential_option_2': '被打擊後無敵時間 +2秒', 'potential_option_3': '被擊中時有5% 機率無視 20% 傷害', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000'</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '戒指', 'item_equipment_slot': '戒指4', 'item_name': '銀花戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_description': None, 'item_shape_name': '銀花戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_gender': None, 'item_total_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 110}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +12', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '3', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊時有4%機率在7秒間無敵', 'potential_option_2': 'DEX +10%', 'potential_option_3': 'STR +16', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ig</t>
+          <t>[{'item_equipment_part': '戒指', 'item_equipment_slot': '戒指4', 'item_name': '銀花戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_description': None, 'item_shape_name': '銀花戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIGKI', 'item_gender': None, 'item_total_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 110}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +12', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '3', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'MaxHP +300', 'potential_option_2': '被打擊後無敵時間 +2秒', 'potential_option_3': '被擊中時有5% 機率無視 20% 傷害', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damag</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊時有4%機率在7秒間無敵', 'potential_option_2': 'DEX +10%', 'potential_option_3': 'STR +16', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000', 'attack_po</t>
+          <t>[{'item_equipment_part': '帽子', 'item_equipment_slot': '帽子', 'item_name': '航海師劍士頭盔', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_description': None, 'item_shape_name': '航海師劍士頭盔', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPCPDMD', 'item_gender': None, 'item_total_option': {'str': '170', 'dex': '88', 'int': '22', 'luk': '0', 'max_hp': '1430', 'max_mp': '0', 'attack_power': '10', 'magic_power': '0', 'armor': '1005', 'speed': '2', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '2', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '45', 'dex': '45', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '400', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '10', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +11', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': '跳躍力 +4', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '5', 'int': '19', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '2', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '11', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '1', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '73', 'dex': '1', 'int': '3', 'luk': '0', 'max_hp': '1200', 'max_mp': '0', 'attack_power': '7', 'magic_power': '0', 'armor': '102', 'speed': '2', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '503', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '臉飾', 'item_equipment_slot': '臉飾', 'item_name': '暮光印記', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_description': None, 'item_shape_name': '暮光印記', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPDJALG', 'item_gender': None, 'item_total_option': {'str': '71', 'dex': '55', 'int': '50', 'luk': '62', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '12', 'armor': '227', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '5', 'dex': '5', 'int': '5', 'luk': '5', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '5', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '罕見', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +6%', 'potential_option_2': '全屬性 +3%', 'potential_option_3': '全屬性 +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '防禦力 +60', 'additional_potential_option_3': 'DEX +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '24', 'dex': '8', 'int': '0', 'luk': '8', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '0', 'armor': '8', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '4', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '5', 'dex': '5', 'int': '8', 'luk': '12', 'max_hp': '0', 'max_mp': '0', 'attack_power': '11', 'magic_power': '7', 'armor': '6', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '113', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '眼飾', 'item_equipment_slot': '眼飾', 'item_name': '水中信紙眼飾', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_description': None, 'item_shape_name': '水中信紙眼飾', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPAJFNA', 'item_gender': None, 'item_total_option': {'str': '21', 'dex': '15', 'int': '15', 'luk': '9', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '1', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '6', 'dex': '6', 'int': '6', 'luk': '6', 'max_hp': '0', 'max_mp': '0', 'attack_power': '1', 'magic_power': '1', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 100}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'MaxHP +3%', 'potential_option_3': 'STR +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +2%', 'additional_potential_option_2': '魔法攻擊力 +2', 'additional_potential_option_3': 'MaxHP +50', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '9', 'int': '9', 'luk': '3', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '1', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '4', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '耳環', 'item_equipment_slot': '耳環', 'item_name': '頂級培羅德耳環', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_description': '用培羅德核心碎片做成的耳環。好像偶爾會發亮。', 'item_shape_name': '頂級培羅德耳環', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPBJFMC', 'item_gender': None, 'item_total_option': {'str': '46', 'dex': '46', 'int': '46', 'luk': '46', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '188', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '150', 'max_mp': '150', 'attack_power': '10', 'magic_power': '10', 'armor': '100', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +6%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'DEX +12', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '魔法攻擊力 +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '12', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '31', 'dex': '31', 'int': '31', 'luk': '31', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '88', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '上衣', 'item_equipment_slot': '上衣', 'item_name': '永恆劍士鎧甲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_description': None, 'item_shape_name': '永恆劍士鎧甲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPGJDNC', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '94', 'int': '14', 'luk': '28', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': 'MaxHP +300', 'potential_option_2': '被打擊後無敵時間 +2秒', 'potential_option_3': '被擊中時有5% 機率無視 20% 傷害', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '7', 'dex': '7', 'int': '14', 'luk': '28', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '褲/裙', 'item_equipment_slot': '褲/裙', 'item_name': '永恆劍士褲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_description': None, 'item_shape_name': '永恆劍士褲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPEJFGE', 'item_gender': None, 'item_total_option': {'str': '101', 'dex': '87', 'int': '0', 'luk': '38', 'max_hp': '230', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '654', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '50', 'dex': '50', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '325', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '5', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 250}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': None, 'potential_option_flag': 'false', 'potential_option_1': '被擊中時有10% 機率無視 40% 傷害', 'potential_option_2': 'STR +10%', 'potential_option_3': 'STR +10%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': None, 'additional_potential_option_2': None, 'additional_potential_option_3': None, 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '14', 'dex': '0', 'int': '0', 'luk': '38', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '2', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '8', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '329', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '鞋子', 'item_equipment_slot': '鞋子', 'item_name': '航海師劍士鞋', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_description': None, 'item_shape_name': '航海師劍士鞋', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPFIHNB', 'item_gender': None, 'item_total_option': {'str': '114', 'dex': '72', 'int': '40', 'luk': '10', 'max_hp': '720', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '427', 'speed': '26', 'jump': '23', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '20', 'dex': '20', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '5', 'magic_power': '0', 'armor': '150', 'speed': '10', 'jump': '7', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'LUK +4%', 'potential_option_3': 'STR +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +11', 'additional_potential_option_2': 'MaxHP +60', 'additional_potential_option_3': 'INT +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '15', 'dex': '15', 'int': '40', 'luk': '10', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '217', 'speed': '16', 'jump': '16'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手套', 'item_equipment_slot': '手套', 'item_name': '神祕冥界幽靈騎士手套', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_description': None, 'item_shape_name': '神祕冥界幽靈騎士手套', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEPKJBHE', 'item_gender': None, 'item_total_option': {'str': '78', 'dex': '79', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '18', 'magic_power': '0', 'armor': '507', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '40', 'dex': '40', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '爆擊傷害 +8%', 'potential_option_2': 'MaxHP +230', 'potential_option_3': 'HP恢復道具及恢復技能效率 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +3%', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': '魔法攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '1', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '5', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '1', 'dex': '2', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '3', 'magic_power': '0', 'armor': '2', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '6', 'magic_power': '0', 'armor': '255', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '披風', 'item_equipment_slot': '披風', 'item_name': '航海師劍士斗篷', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_description': None, 'item_shape_name': '航海師劍士斗篷', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEOCJAJE', 'item_gender': None, 'item_total_option': {'str': '94', 'dex': '52', 'int': '15', 'luk': '15', 'max_hp': '950', 'max_mp': '480', 'attack_power': '3', 'magic_power': '2', 'armor': '655', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '3', 'damage': '0', 'equipment_level_decrease': 15, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '15', 'dex': '15', 'int': '15', 'luk': '15', 'max_hp': '0', 'max_mp': '0', 'attack_power': '2', 'magic_power': '2', 'armor': '250', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 160}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'STR +7%', 'potential_option_2': 'STR +4%', 'potential_option_3': 'MaxMP +4%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'INT +11', 'additional_potential_option_2': 'DEX +6', 'additional_potential_option_3': '物理攻擊力 +3', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '480', 'attack_power': '0', 'magic_power': '0', 'armor': '27', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '3', 'equipment_level_decrease': 15}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '6', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '2', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '42', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '720', 'max_mp': '0', 'attack_power': '1', 'magic_power': '0', 'armor': '60', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '0', 'luk': '0', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '318', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '手鐲', 'item_equipment_slot': '輔助武器', 'item_name': '不滅的手鐲', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_description': None, 'item_shape_name': '不滅的手鐲', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEMHPHOG', 'item_gender': None, 'item_total_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '14', 'dex': '14', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '9', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 140}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': 'DEX +12%', 'potential_option_2': '攻擊Boss怪物時傷害 +30%', 'potential_option_3': '攻擊Boss怪物時傷害 +30%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +12', 'additional_potential_option_2': '跳躍力 +4', 'additional_potential_option_3': '物理攻擊力 +6', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '0', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '調節器', 'item_equipment_slot': '武器', 'item_name': '神祕冥界幽靈調節器', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_description': None, 'item_shape_name': '神祕冥界幽靈調節器', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KENDIHPJ', 'item_gender': None, 'item_total_option': {'str': '260', 'dex': '260', 'int': '120', 'luk': '120', 'max_hp': '255', 'max_mp': '2055', 'attack_power': '631', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'damage': '2', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '100', 'dex': '100', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '295', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '30', 'ignore_monster_armor': '20', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 200}, 'potential_option_grade': '傳說', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '物理攻擊力 +13%', 'potential_option_2': '傷害 +13%', 'potential_option_3': '攻擊Boss怪物時傷害 +40%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': '物理攻擊力 +4%', 'additional_potential_option_2': '移動速度 +6', 'additional_potential_option_3': '防禦力 +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '1800', 'attack_power': '54', 'magic_power': '0', 'armor': '11', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '2', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '9', 'cuttable_count': '10', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '0', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': '1', 'soul_weapon_level': '3', 'soul_weapon_power_increase': '23', 'soul_weapon_option': 'MaxMP +200', 'item_etc_option': {'str': '90', 'dex': '90', 'int': '90', 'luk': '90', 'max_hp': '0', 'max_mp': '0', 'attack_power': '108', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '17', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '70', 'dex': '70', 'int': '30', 'luk': '30', 'max_hp': '255', 'max_mp': '255', 'attack_power': '174', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指1', 'item_name': '頂級培羅德戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_description': '用培羅德核心碎片做成的戒指。', 'item_shape_name': '頂級培羅德戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODIHJE', 'item_gender': None, 'item_total_option': {'str': '47', 'dex': '47', 'int': '47', 'luk': '47', 'max_hp': '480', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '306', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'damage': '0', 'equipment_level_decrease': 0, 'max_hp_rate': '0', 'max_mp_rate': '0'}, 'item_base_option': {'str': '10', 'dex': '10', 'int': '10', 'luk': '10', 'max_hp': '250', 'max_mp': '250', 'attack_power': '8', 'magic_power': '8', 'armor': '150', 'speed': '10', 'jump': '0', 'boss_damage': '0', 'ignore_monster_armor': '0', 'all_stat': '0', 'max_hp_rate': '0', 'max_mp_rate': '0', 'base_equipment_level': 150}, 'potential_option_grade': '稀有', 'additional_potential_option_grade': '特殊', 'potential_option_flag': 'false', 'potential_option_1': '全屬性 +3%', 'potential_option_2': 'STR +3%', 'potential_option_3': 'STR +3%', 'additional_potential_option_flag': 'false', 'additional_potential_option_1': 'STR +10', 'additional_potential_option_2': '魔法攻擊力 +3', 'additional_potential_option_3': 'MaxMP +60', 'equipment_level_increase': 0, 'item_exceptional_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'exceptional_upgrade': 0}, 'item_add_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0', 'boss_damage': '0', 'damage': '0', 'all_stat': '0', 'equipment_level_decrease': 0}, 'growth_exp': 0, 'growth_level': 0, 'scroll_upgrade': '0', 'cuttable_count': '255', 'golden_hammer_flag': '0', 'scroll_resilience_count': '0', 'scroll_upgradeable_count': '7', 'soul_name': None, 'soul_option': None, 'soul_weapon_grade': None, 'soul_weapon_level': None, 'soul_weapon_power_increase': None, 'soul_weapon_option': None, 'item_etc_option': {'str': '0', 'dex': '0', 'int': '0', 'luk': '0', 'max_hp': '0', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '0', 'speed': '0', 'jump': '0'}, 'starforce': '14', 'starforce_scroll_flag': '未套用', 'item_starforce_option': {'str': '37', 'dex': '37', 'int': '37', 'luk': '37', 'max_hp': '230', 'max_mp': '0', 'attack_power': '0', 'magic_power': '0', 'armor': '156', 'speed': '0', 'jump': '0'}, 'special_ring_level': 0, 'date_expire': None, 'freestyle_flag': '0'}, {'item_equipment_part': '戒指', 'item_equipment_slot': '戒指2', 'item_name': '宇宙戒指', 'item_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_description': '裝有宇宙秩序的戒指。聽說和宇宙原子□生反應的話，力量會變□大。\r\n可賦予潛在能力及附加潛在能力', 'item_shape_name': '宇宙戒指', 'item_shape_icon': 'https://open.api.nexon.com/static/maplestorytw/item/icon/KEODPEOC', 'item_gender': None, 'item_total_option': {'str': '20', 'dex': '20', 'int': '20', 'luk': '20', 'max_hp': '2000', 'max_mp': '2000'</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">

--- a/character_data_formatted.xlsx
+++ b/character_data_formatted.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\\r\\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\\r\\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\\r\\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\\r\\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\\r\\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\\r\\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\\r\\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\\r\\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\\r\\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\\n套用主武器的攻擊力和魔力中較高的值\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\\r\\n實體化在楓之谷成就選擇的徽章。\\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯I', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯跳躍並發射衝擊波攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯跳躍：對最多10名敵人造成500%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 4, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKA', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯II', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯啃咬前方，攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯撕咬：對最多10名敵人造成550%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 2, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKB', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯III', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯以鋒利的爪子攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯利爪：對最多10名敵人造成600%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKC', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯IV', 'skill_description': '[等級上限 : 4]\\r\\n艾拉諾斯猛烈咆哮，攻擊周圍敵人。\\n\\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\\n\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\\n\\n召喚艾拉諾斯70秒。\\n艾拉諾斯咆哮：對最多10名敵人造成650%傷害，攻擊6次\\n冷卻時間60秒\\n艾拉諾斯成長時攻擊範圍與傷害增加。\\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 4, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKD', 'skill_effect_next': None}, {'skill_name': '幻影魔法', 'skill_description': '[等級上限 : 1]\\r\\n由記憶與回憶的幻影交織而成的神祕魔法。', 'skill_level': 1, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKF', 'skill_effect_next': None}, {'skill_name': '咆哮的艾拉諾斯', 'skill_description': '[最高等級：1]\\n每當消滅等級範圍怪物時可累積計量表，\\n當計量表全滿時，即可發動&lt;咆哮的艾拉諾斯&gt;。\\n\\n每日&lt;咆哮的艾拉諾斯&gt;發動次數達到20次時\\n結束。\\n\\n活動期間結束後將無法使用。\\n\\n - 變更開關\\n右擊新手技能欄&lt;咆哮的艾拉諾斯&gt;技能\\n - 變更自動/手動\\n右擊UI的&lt;咆哮的艾拉諾斯&gt;技能\\n', 'skill_level': 1, 'skill_effect': '\\n\\n&lt;咆哮的艾拉諾斯II&gt;最多對15名敵人以3000%傷害攻擊1次的\\n爆炸發動6次的技能發動6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEE', 'skill_effect_next': None}, {'skill_name': '古代力量', 'skill_description': '[等級上限 : 1]\\r\\n隨著透過調查逐步找回力量，將會越來越強。', 'skill_level': 1, 'skill_effect': '攻擊力/魔力增加 30\r\n攻擊BOSS怪物時傷害增加40%\r\n無視怪物防禦率增加40%\r\nBuff持續時間增加20%\r\n攻擊一般怪物時傷害增加 20%\r\n經驗值獲得量增加12.5%\r\n消滅BOSS怪物時獲得的靈魂艾爾達氣息增加100%\r\n從怪物公園退場時獲得的經驗值增加50%\r\n完成奧術之河每日任務時，獲得經驗值增加50%、獲得符文增加20個\r\n完成格蘭蒂斯每日任務時，增加50%獲得的經驗值、9個獲得的符文\r\n真實之力增加40\r\n從怪物公園退場時獲得的經驗值增加30%\r\n智慧餘響經驗值增加200%\r\n消滅BOSS怪物時，獲得的靈魂艾爾達氣息增加40%\r\n完成奧術之河每日任務時，增加20%獲得的經驗值、4個獲得的符文\r\n完成格蘭蒂斯每日任務時，增加20%獲得的經驗值、3個獲得的符文\r\n狩獵場獲得靈魂艾爾達氣息100%增加\r\n寶藏獵人經驗值獲得量100%增加\r\n攻擊BOSS怪物時傷害增加10%\r\n史詩副本基本經驗值獎勵獲得量150%增加', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEH', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '再訪', 'skill_description': '[等級上限 : 1]\r\n重訪藝術之都市，里斯托尼亞。', 'skill_level': 1, 'skill_effect': '消耗MP30，使用時可移動至里斯托尼亞。\n冷卻時間600秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMA', 'skill_effect_next': None}, {'skill_name': '獨門咒語', 'skill_description': '[最高等級：1]\n提升周圍所有角色的攻擊力和魔力。', 'skill_level': 1, 'skill_effect': '消耗30MP，使攻擊力、魔力增加4%，持續2400秒\n冷卻時間為300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPBMF', 'skill_effect_next': None}, {'skill_name': '魔法迴路', 'skill_description': '[等級上限 : 1]\r\n具有魔力之翼的雷普可透過特殊的魔力迴路自由轉換攻擊力和魔力。阿戴爾因為過度使用魔力迴路，造成迴路相當部分燒毀，導致轉換率下降。', 'skill_level': 1, 'skill_effect': '除了武器外，所有裝備的魔法攻擊力以 35%轉換為攻擊力。但不會適用套裝效果，可轉換裝備中的武器基本攻擊力的 15%。', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLJ', 'skill_effect_next': None}, {'skill_name': '信念', 'skill_description': '[等級上限 : 10]\r\n尋找失去的記憶明白過去的真相。', 'skill_level': 10, 'skill_effect': '增加爆擊傷害10%、攻擊力10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBMG', 'skill_effect_next': None}, {'skill_name': '精靈的祝福', 'skill_description': '[等級上限 : 20]\r\n只要將其他角色培育到10級以上，技能點數就會增加1。但是，可以發動精靈的祝福與女皇的祝福中較好的效果。', 'skill_level': 20, 'skill_effect': '增加攻擊力20、魔力20', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBNC', 'skill_effect_next': None}, {'skill_name': '女皇的祝福', 'skill_description': '[等級上限 : 30]\r\n只要將其他西格諾斯角色和米哈逸角色培育到5級以上，技能點數就會增加1。但是精靈的祝福和女皇的祝福中以最強的效果啟動。\r\n其他西格諾斯和米哈逸角色的高貴的精神，最高等級最多可擴大至30。', 'skill_level': 30, 'skill_effect': '增加攻擊力30、魔力30', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOBLD', 'skill_effect_next': None}, {'skill_name': '聯盟的意志', 'skill_description': '[等級上限 : 1]\r\n依據聯盟的意志，發揮強大力量。', 'skill_level': 1, 'skill_effect': '永久提升力量5、敏捷5、智力5、幸運5、攻擊力5、魔力5', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFOAFA', 'skill_effect_next': None}, {'skill_name': '管理連結技能', 'skill_description': '[等級上限 : 1]\r\n可以傳授世界裡其他角色的連結技能，或解除目前傳授中的連結技能。', 'skill_level': 1, 'skill_effect': '管理我的連結技能傳授狀態', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKCLFPDJB', 'skill_effect_next': None}, {'skill_name': '武器泡泡 - S環', 'skill_description': '[等級上限 : 4]\r\n一定時間內依照主武器攻擊或魔力的部分值增加STR。不會得到冷卻時間初始化的效果。', 'skill_level': 4, 'skill_effect': '消耗HP 600，15秒 間STR增加裝備中的主武器攻擊力或魔力的260%，惡魔復仇者HP增加相應數值的17.5倍\n套用主武器的攻擊力和魔力中較高的值\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHPFLA', 'skill_effect_next': None}, {'skill_name': '楓之谷徽章', 'skill_description': '[等級上限 : 1]\r\n實體化在楓之谷成就選擇的徽章。\n實體化的徽章會在角色周圍顯示一段時間後消失。依照成就等級與完成的成就，可選擇各種徽章並實體化。', 'skill_level': 1, 'skill_effect': '冷卻時間5秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHMCOD', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯I', 'skill_description': '[等級上限 : 4]\r\n艾拉諾斯跳躍並發射衝擊波攻擊周圍敵人。\n\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\n\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\n\n召喚艾拉諾斯70秒。\n艾拉諾斯跳躍：對最多10名敵人造成500%傷害，攻擊6次\n冷卻時間60秒\n艾拉諾斯成長時攻擊範圍與傷害增加。\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 4, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKA', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯II', 'skill_description': '[等級上限 : 4]\r\n艾拉諾斯啃咬前方，攻擊周圍敵人。\n\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\n\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\n\n召喚艾拉諾斯70秒。\n艾拉諾斯撕咬：對最多10名敵人造成550%傷害，攻擊6次\n冷卻時間60秒\n艾拉諾斯成長時攻擊範圍與傷害增加。\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 2, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKB', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯III', 'skill_description': '[等級上限 : 4]\r\n艾拉諾斯以鋒利的爪子攻擊周圍敵人。\n\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\n\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\n\n召喚艾拉諾斯70秒。\n艾拉諾斯利爪：對最多10名敵人造成600%傷害，攻擊6次\n冷卻時間60秒\n艾拉諾斯成長時攻擊範圍與傷害增加。\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 3, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKC', 'skill_effect_next': None}, {'skill_name': '艾拉諾斯IV', 'skill_description': '[等級上限 : 4]\r\n艾拉諾斯猛烈咆哮，攻擊周圍敵人。\n\n艾拉諾斯無法在空中召喚，且攻擊處於反射狀態的敵人時不會受到傷害。\n\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影僕從、引雷、高貴血統、虛擬投影時，將不套用攻擊次數增加效果，改為套用相同數值的最終傷害增加效果。\n\n召喚艾拉諾斯70秒。\n艾拉諾斯咆哮：對最多10名敵人造成650%傷害，攻擊6次\n冷卻時間60秒\n艾拉諾斯成長時攻擊範圍與傷害增加。\n不受冷卻時間重置效果與Buff持續時間增加效果影響。', 'skill_level': 4, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKD', 'skill_effect_next': None}, {'skill_name': '幻影魔法', 'skill_description': '[等級上限 : 1]\r\n由記憶與回憶的幻影交織而成的神祕魔法。', 'skill_level': 1, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBKF', 'skill_effect_next': None}, {'skill_name': '咆哮的艾拉諾斯', 'skill_description': '[最高等級：1]\n每當消滅等級範圍怪物時可累積計量表，\n當計量表全滿時，即可發動&lt;咆哮的艾拉諾斯&gt;。\n\n每日&lt;咆哮的艾拉諾斯&gt;發動次數達到20次時\n結束。\n\n活動期間結束後將無法使用。\n\n - 變更開關\n右擊新手技能欄&lt;咆哮的艾拉諾斯&gt;技能\n - 變更自動/手動\n右擊UI的&lt;咆哮的艾拉諾斯&gt;技能\n', 'skill_level': 1, 'skill_effect': '\n\n&lt;咆哮的艾拉諾斯II&gt;最多對15名敵人以3000%傷害攻擊1次的\n爆炸發動6次的技能發動6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEE', 'skill_effect_next': None}, {'skill_name': '古代力量', 'skill_description': '[等級上限 : 1]\r\n隨著透過調查逐步找回力量，將會越來越強。', 'skill_level': 1, 'skill_effect': '攻擊力/魔力增加 30\r\n攻擊BOSS怪物時傷害增加40%\r\n無視怪物防禦率增加40%\r\nBuff持續時間增加20%\r\n攻擊一般怪物時傷害增加 20%\r\n經驗值獲得量增加12.5%\r\n消滅BOSS怪物時獲得的靈魂艾爾達氣息增加100%\r\n從怪物公園退場時獲得的經驗值增加50%\r\n完成奧術之河每日任務時，獲得經驗值增加50%、獲得符文增加20個\r\n完成格蘭蒂斯每日任務時，增加50%獲得的經驗值、9個獲得的符文\r\n真實之力增加40\r\n從怪物公園退場時獲得的經驗值增加30%\r\n智慧餘響經驗值增加200%\r\n消滅BOSS怪物時，獲得的靈魂艾爾達氣息增加40%\r\n完成奧術之河每日任務時，增加20%獲得的經驗值、4個獲得的符文\r\n完成格蘭蒂斯每日任務時，增加20%獲得的經驗值、3個獲得的符文\r\n狩獵場獲得靈魂艾爾達氣息100%增加\r\n寶藏獵人經驗值獲得量100%增加\r\n攻擊BOSS怪物時傷害增加10%\r\n史詩副本基本經驗值獎勵獲得量150%增加', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KFHCLHKBEH', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[{'skill_name': '平砍', 'skill_description': '[等級上限 : 10]\\r\\n用魔力形成的劍朝前方砍擊。', 'skill_level': 10, 'skill_effect': '消耗MP12，最多對5名敵人以85%傷害攻擊4次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBMA', 'skill_effect_next': None}, {'skill_name': '碎片', 'skill_description': '[等級上限 : 20]\\r\\n製造魔力碎片，當碎片感應到敵人就會朝敵人飛去。即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。', 'skill_level': 20, 'skill_effect': '消耗20 MP，生成5個魔力碎片，每個碎片將對最多1名敵人造成80%傷害3次\\n冷卻時間：6秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBMB', 'skill_effect_next': None}, {'skill_name': '閃擊', 'skill_description': '[等級上限 : 10]\\r\\n以優雅的身姿如閃光般穿越敵人。', 'skill_level': 10, 'skill_effect': '消耗MP11，以160%傷害對最多4名敵人進行攻擊', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBMG', 'skill_effect_next': None}, {'skill_name': '跳躍', 'skill_description': '[等級上限 : 5]\\r\\n跳躍時再跳躍一次就可以遠距離移動。同時按著「上」方向鍵即可往上方移動。', 'skill_level': 5, 'skill_effect': '消耗MP5，跳躍一段距離', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBMC', 'skill_effect_next': None}, {'skill_name': '懸浮', 'skill_description': '[等級上限 : 1]\\r\\n下定決心犧牲自己保護重要的人。\\n若在空中使用技能，或連續按兩下「上」方向鍵，即可釋放魔力進行短暫的懸浮，並且可使用空中技能。再使用一次或者使用移動技能即可取消懸浮。\\n指令上鎖：右擊滑鼠', 'skill_level': 1, 'skill_effect': '消耗MP20，進行懸浮一段時間', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBME', 'skill_effect_next': None}, {'skill_name': '入門', 'skill_description': '[等級上限 : 19]\\r\\n鍛鍊戰士的基礎。', 'skill_level': 19, 'skill_effect': '增加30攻擊力、200防禦力、1000最大HP\\n增加17移動速度、10跳躍力、10最大移動速度、60%格擋機率\\n所受傷害減少10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHOBMF', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '平砍', 'skill_description': '[等級上限 : 10]\r\n用魔力形成的劍朝前方砍擊。', 'skill_level': 10, 'skill_effect': '消耗MP12，最多對5名敵人以85%傷害攻擊4次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBMA', 'skill_effect_next': None}, {'skill_name': '碎片', 'skill_description': '[等級上限 : 20]\r\n製造魔力碎片，當碎片感應到敵人就會朝敵人飛去。即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。', 'skill_level': 20, 'skill_effect': '消耗20 MP，生成5個魔力碎片，每個碎片將對最多1名敵人造成80%傷害3次\n冷卻時間：6秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBMB', 'skill_effect_next': None}, {'skill_name': '閃擊', 'skill_description': '[等級上限 : 10]\r\n以優雅的身姿如閃光般穿越敵人。', 'skill_level': 10, 'skill_effect': '消耗MP11，以160%傷害對最多4名敵人進行攻擊', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBMG', 'skill_effect_next': None}, {'skill_name': '跳躍', 'skill_description': '[等級上限 : 5]\r\n跳躍時再跳躍一次就可以遠距離移動。同時按著「上」方向鍵即可往上方移動。', 'skill_level': 5, 'skill_effect': '消耗MP5，跳躍一段距離', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBMC', 'skill_effect_next': None}, {'skill_name': '懸浮', 'skill_description': '[等級上限 : 1]\r\n下定決心犧牲自己保護重要的人。\n若在空中使用技能，或連續按兩下「上」方向鍵，即可釋放魔力進行短暫的懸浮，並且可使用空中技能。再使用一次或者使用移動技能即可取消懸浮。\n指令上鎖：右擊滑鼠', 'skill_level': 1, 'skill_effect': '消耗MP20，進行懸浮一段時間', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHPBME', 'skill_effect_next': None}, {'skill_name': '入門', 'skill_description': '[等級上限 : 19]\r\n鍛鍊戰士的基礎。', 'skill_level': 19, 'skill_effect': '增加30攻擊力、200防禦力、1000最大HP\n增加17移動速度、10跳躍力、10最大移動速度、60%格擋機率\n所受傷害減少10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDLHOBMF', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[{'skill_name': '乙太', 'skill_description': '[等級上限 : 1]\\r\\n煉製魔力獲得特別的乙太。可以利用乙太創造具有意志的乙太之劍。\\n每隔一段時間可從周圍的魔力獲得少量乙太，攻擊敵人時也可獲得。', 'skill_level': 1, 'skill_effect': '每隔一段時間獲得5乙太，當觸發技能命中時可獲得12個乙太，消滅一般怪物時，依據消滅怪物的數量獲得3個乙太，最多可獲得300個。\\n創造啟動時，每100個乙太可創造2把乙太之劍，最多可創造4把', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBNH', 'skill_effect_next': None}, {'skill_name': '乙太結晶', 'skill_description': '[等級上限 : 1]\\r\\n乙太之劍攻擊敵人時，四散的乙太有時候會聚集起來形成結晶。使用魔劍共鳴時可發動共鳴，朝有結晶的地方突進。', 'skill_level': 1, 'skill_effect': '結晶可維持30秒，地圖上最多可存在7個結晶\\n當結晶數量超過可存在數量上限的時，剩餘持續時間最短的結晶將消失\\n已有結晶的位置附近、特定踏板及無法前往的踏板附近不會生成結晶\\n重新生成冷卻時間：4秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBMC', 'skill_effect_next': None}, {'skill_name': '刺擊', 'skill_description': '[等級上限 : 20]\\r\\n[觸發技能] 形成多把長劍刺向前方。', 'skill_level': 20, 'skill_effect': '消耗MP25，最多對6名敵人以80%傷害攻擊8次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHPBMA', 'skill_effect_next': None}, {'skill_name': '穿刺', 'skill_description': '[等級上限 : 10]\\r\\n創造乙太之劍，並強力射出。可往8方向擊飛，搭配方向鍵使用時，可朝該方向發射。\\n到達射程距離極限時，乙太之劍便將會消失，並且留下乙太結晶。，並且留下乙太結晶。當穿刺形成乙太結晶時，若該處已經有結晶，則消滅之前的結晶並重新形成，重新形成無視冷卻時間。\\n可連接魔劍共鳴，但連接時，無法留下乙太結晶。', 'skill_level': 10, 'skill_effect': '消耗45 MP、15乙太\\n對最多6名敵人造成85%傷害6次\\n冷卻時間：7秒  ', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHPBMB', 'skill_effect_next': None}, {'skill_name': '魔劍共鳴', 'skill_description': '[等級上限 : 10]\\r\\n製造由魔力組成的巨劍後，使其和乙太結晶共鳴，朝結晶所在的地方突進。可透過8個方向使用，和方向鍵一起使用時，可朝位於該方向最近的結晶突進。\\n射程距離內必須有乙太結晶，或者從穿刺進行連接才可使用。\\n從穿刺進行連接使用時可縮短巨劍形成時間，朝投射乙太之劍的方向突進。\\r\\n所需技能：穿刺 3等級以上', 'skill_level': 10, 'skill_effect': '和魔劍共鳴的乙太結晶消失\\n最多以105%的傷害攻擊6名敵人6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHPBMD', 'skill_effect_next': None}, {'skill_name': '推進器', 'skill_description': '[等級上限 : 10]\\r\\n消耗MP後一段時間內增加調節器的攻擊速度2階段。\\r\\n所需技能：精通 5等級以上', 'skill_level': 10, 'skill_effect': '消耗MP10，200秒內調節器的攻擊速度增加', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHPBMF', 'skill_effect_next': None}, {'skill_name': '創造', 'skill_description': '[等級上限 : 10]\\r\\n以目前持有的乙太在自身周圍創造乙太之劍，乙太之劍的數量會自動根據乙太的增減進行調整。\\n創造出來的乙太之劍會自動攻擊周圍的敵人，即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。\\n乙太之劍特效開關：右擊滑鼠', 'skill_level': 10, 'skill_effect': '觸發技能命中時每9.5秒最多對10名敵人以200%的傷害進行攻擊，進行3轉/4轉轉職時，再次攻擊冷卻時間各減少4秒\\n每1把乙太之劍攻擊1次\\n攻擊命中時有30%機率形成乙太結晶\\n', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBMG', 'skill_effect_next': None}, {'skill_name': '奇蹟', 'skill_description': '[等級上限 : 10]\\r\\n攻擊時自動生成碎片。\\r\\n所需技能：碎片 20等級以上', 'skill_level': 10, 'skill_effect': '觸發技能命中時每8秒形成，形成時消耗MP25\\n碎片的傷害增加30%p', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBND', 'skill_effect_next': None}, {'skill_name': '精通', 'skill_description': '[等級上限 : 10]\\r\\n增加調節器的熟練度、攻擊力、爆擊傷害。', 'skill_level': 10, 'skill_effect': '調節器熟練度增加至50%\\n攻擊力增加 30\\n爆擊傷害增加11%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBNE', 'skill_effect_next': None}, {'skill_name': '特性培養', 'skill_description': '[等級上限 : 9]\\r\\n具備生存所需的資質。另外，永久增加最終傷害和無視怪物防禦率。', 'skill_level': 9, 'skill_effect': '每5秒恢復最大HP/MP的4%，戰鬥過程中亦可恢復\\n最終傷害增加10%、無視怪物防禦率增加10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBNF', 'skill_effect_next': None}, {'skill_name': '鍛鍊', 'skill_description': '[等級上限 : 5]\\r\\n透過鍛鍊身體增加力量。', 'skill_level': 5, 'skill_effect': '增加60力量', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBNG', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '乙太', 'skill_description': '[等級上限 : 1]\r\n煉製魔力獲得特別的乙太。可以利用乙太創造具有意志的乙太之劍。\n每隔一段時間可從周圍的魔力獲得少量乙太，攻擊敵人時也可獲得。', 'skill_level': 1, 'skill_effect': '每隔一段時間獲得5乙太，當觸發技能命中時可獲得12個乙太，消滅一般怪物時，依據消滅怪物的數量獲得3個乙太，最多可獲得300個。\n創造啟動時，每100個乙太可創造2把乙太之劍，最多可創造4把', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBNH', 'skill_effect_next': None}, {'skill_name': '乙太結晶', 'skill_description': '[等級上限 : 1]\r\n乙太之劍攻擊敵人時，四散的乙太有時候會聚集起來形成結晶。使用魔劍共鳴時可發動共鳴，朝有結晶的地方突進。', 'skill_level': 1, 'skill_effect': '結晶可維持30秒，地圖上最多可存在7個結晶\n當結晶數量超過可存在數量上限的時，剩餘持續時間最短的結晶將消失\n已有結晶的位置附近、特定踏板及無法前往的踏板附近不會生成結晶\n重新生成冷卻時間：4秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBMC', 'skill_effect_next': None}, {'skill_name': '刺擊', 'skill_description': '[等級上限 : 20]\r\n[觸發技能] 形成多把長劍刺向前方。', 'skill_level': 20, 'skill_effect': '消耗MP25，最多對6名敵人以80%傷害攻擊8次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHPBMA', 'skill_effect_next': None}, {'skill_name': '穿刺', 'skill_description': '[等級上限 : 10]\r\n創造乙太之劍，並強力射出。可往8方向擊飛，搭配方向鍵使用時，可朝該方向發射。\n到達射程距離極限時，乙太之劍便將會消失，並且留下乙太結晶。，並且留下乙太結晶。當穿刺形成乙太結晶時，若該處已經有結晶，則消滅之前的結晶並重新形成，重新形成無視冷卻時間。\n可連接魔劍共鳴，但連接時，無法留下乙太結晶。', 'skill_level': 10, 'skill_effect': '消耗45 MP、15乙太\n對最多6名敵人造成85%傷害6次\n冷卻時間：7秒  ', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHPBMB', 'skill_effect_next': None}, {'skill_name': '魔劍共鳴', 'skill_description': '[等級上限 : 10]\r\n製造由魔力組成的巨劍後，使其和乙太結晶共鳴，朝結晶所在的地方突進。可透過8個方向使用，和方向鍵一起使用時，可朝位於該方向最近的結晶突進。\n射程距離內必須有乙太結晶，或者從穿刺進行連接才可使用。\n從穿刺進行連接使用時可縮短巨劍形成時間，朝投射乙太之劍的方向突進。\r\n所需技能：穿刺 3等級以上', 'skill_level': 10, 'skill_effect': '和魔劍共鳴的乙太結晶消失\n最多以105%的傷害攻擊6名敵人6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHPBMD', 'skill_effect_next': None}, {'skill_name': '推進器', 'skill_description': '[等級上限 : 10]\r\n消耗MP後一段時間內增加調節器的攻擊速度2階段。\r\n所需技能：精通 5等級以上', 'skill_level': 10, 'skill_effect': '消耗MP10，200秒內調節器的攻擊速度增加', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHPBMF', 'skill_effect_next': None}, {'skill_name': '創造', 'skill_description': '[等級上限 : 10]\r\n以目前持有的乙太在自身周圍創造乙太之劍，乙太之劍的數量會自動根據乙太的增減進行調整。\n創造出來的乙太之劍會自動攻擊周圍的敵人，即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。\n乙太之劍特效開關：右擊滑鼠', 'skill_level': 10, 'skill_effect': '觸發技能命中時每9.5秒最多對10名敵人以200%的傷害進行攻擊，進行3轉/4轉轉職時，再次攻擊冷卻時間各減少4秒\n每1把乙太之劍攻擊1次\n攻擊命中時有30%機率形成乙太結晶\n', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBMG', 'skill_effect_next': None}, {'skill_name': '奇蹟', 'skill_description': '[等級上限 : 10]\r\n攻擊時自動生成碎片。\r\n所需技能：碎片 20等級以上', 'skill_level': 10, 'skill_effect': '觸發技能命中時每8秒形成，形成時消耗MP25\n碎片的傷害增加30%p', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBND', 'skill_effect_next': None}, {'skill_name': '精通', 'skill_description': '[等級上限 : 10]\r\n增加調節器的熟練度、攻擊力、爆擊傷害。', 'skill_level': 10, 'skill_effect': '調節器熟練度增加至50%\n攻擊力增加 30\n爆擊傷害增加11%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBNE', 'skill_effect_next': None}, {'skill_name': '特性培養', 'skill_description': '[等級上限 : 9]\r\n具備生存所需的資質。另外，永久增加最終傷害和無視怪物防禦率。', 'skill_level': 9, 'skill_effect': '每5秒恢復最大HP/MP的4%，戰鬥過程中亦可恢復\n最終傷害增加10%、無視怪物防禦率增加10%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBNF', 'skill_effect_next': None}, {'skill_name': '鍛鍊', 'skill_description': '[等級上限 : 5]\r\n透過鍛鍊身體增加力量。', 'skill_level': 5, 'skill_effect': '增加60力量', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKHOBNG', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[{'skill_name': '十字斬', 'skill_description': '[等級上限 : 20]\\r\\n[觸發技能] 以魔力形成2把長劍進行交叉砍擊。', 'skill_level': 20, 'skill_effect': '消耗MP35，最多對6名敵人以220%傷害攻擊6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMA', 'skill_effect_next': None}, {'skill_name': '追蹤', 'skill_description': '[等級上限 : 20]\\r\\n以創造生成乙太之劍，命令其追擊敵方。必須有以創造生成的乙太之劍才可使用。\\n乙太之劍只會在阿戴爾附近移動。當距離變遠時，乙太之劍會移動到近處追擊新敵方。\\n即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害，只有在阿戴爾處於戰鬥狀態時才會追擊敵方。\\n追擊中的乙太之劍消失時，可比照剩餘的持續時間依比例獲得乙太。\\r\\n所需技能：創造 10等級以上', 'skill_level': 20, 'skill_effect': '消耗40 MP、100乙太\\n每把乙太之劍可存在40秒，並造成240%傷害2次\\n最多可對4把乙太之劍下達命令，當下達命令的數量超過可命令數量上限時，剩餘持續時間最短的乙太之劍將消失\\n攻擊命中時，有15%機率生成乙太結晶\\n冷卻時間：0.50秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMD', 'skill_effect_next': None}, {'skill_name': '回歸', 'skill_description': '[等級上限 : 20]\\r\\n讓下達追蹤命令的所有乙太之劍返回。乙太之劍將直線返回施展技能的地點，並在攻擊路徑上的敵人後，停留在移動位置上一段時間。使用瞄準模式後，乙太之劍就會揮向刻有死亡標記的敵人。但僅限在追蹤攻擊範圍內生效。須有因追蹤而正在追蹤敵人的乙太之劍才能使用。\\n回歸發動時，乙太之劍的持續時間將不消耗。回歸攻擊即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害且不受冷卻時間重置效果影響。\\n瞄準模式開關：右擊滑鼠\\r\\n所需技能：追蹤 5等級以上', 'skill_level': 20, 'skill_effect': '消耗50 MP、最多對10名敵人造成4次的260%傷害\\n攻擊命中時，以40%機率生成乙太結晶\\n冷卻時間12秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMC', 'skill_effect_next': None}, {'skill_name': '劍域', 'skill_description': '[等級上限 : 20]\\r\\n設置屬於自己的領域，並創造出無數把劍。即使攻擊，反射攻擊狀態的敵人，也不會遭受傷害。', 'skill_level': 20, 'skill_effect': '消耗120 MP，生成特殊領域7秒，該領域將定期對最多8名敵人造成100%傷害4次\\n持續時間結束時，幻劍將反轉，並對最多12名敵人追加造成550%傷害12次\\n冷卻時間：30秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMB', 'skill_effect_next': None}, {'skill_name': '高潔精神', 'skill_description': '[等級上限 : 10]\\r\\n為了同伴而發揮犧牲自我的高尚精神。在自己周圍生成的領域內，若有包含自己在內的隊員遭受傷害時，代為承受部分傷害並依其傷害量形成護盾。\\n不適用Buff持續時間增加效果，再次使用技能時將立即取消技能。', 'skill_level': 10, 'skill_effect': '消耗200 MP，生成特殊領域20秒\\n代替領域內的隊員承受30%所受傷害，並生成等同80%該傷害量的護盾\\n當代替承受的傷害量高於自己剩餘的HP時，則不代替承受\\n冷卻時間：120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMF', 'skill_effect_next': None}, {'skill_name': '羽翼', 'skill_description': '[等級上限 : 4]\\r\\n如羽毛般輕盈地移動到後方，於空中進行短暫的全體攻擊。\\n使用踐踏以外的觸發技能時也可移動。', 'skill_level': 4, 'skill_effect': '消耗46 MP、30乙太\\n朝後方移動一定距離\\n冷卻時間：8秒\\n[被動效果：增加5移動速度、10跳躍力、10最大移動速度]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBME', 'skill_effect_next': None}, {'skill_name': '上進', 'skill_description': '[等級上限 : 20]\\r\\n以無限的進取心讓進度幅度大躍進', 'skill_level': 20, 'skill_effect': '增加攻擊力30、最終傷害17%、爆擊機率20%\\n碎片的傷害增加10%p\\n創造的傷害增加240%p\\n穿刺的傷害增加100%p\\n魔劍共鳴的傷害增加115%p', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGOBMG', 'skill_effect_next': None}, {'skill_name': '耐性', 'skill_description': '[等級上限 : 10]\\r\\n培養耐性以面對各種危機。另外，永久增加無視怪物防禦率。', 'skill_level': 10, 'skill_effect': '格擋機率增加40%、最大HP增加10%、狀態異常抗性增加30、所有屬性抗性增加30%、無視怪物防禦率增加10%\\n被攻擊時傷害減少20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGOBMH', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '十字斬', 'skill_description': '[等級上限 : 20]\r\n[觸發技能] 以魔力形成2把長劍進行交叉砍擊。', 'skill_level': 20, 'skill_effect': '消耗MP35，最多對6名敵人以220%傷害攻擊6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMA', 'skill_effect_next': None}, {'skill_name': '追蹤', 'skill_description': '[等級上限 : 20]\r\n以創造生成乙太之劍，命令其追擊敵方。必須有以創造生成的乙太之劍才可使用。\n乙太之劍只會在阿戴爾附近移動。當距離變遠時，乙太之劍會移動到近處追擊新敵方。\n即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害，只有在阿戴爾處於戰鬥狀態時才會追擊敵方。\n追擊中的乙太之劍消失時，可比照剩餘的持續時間依比例獲得乙太。\r\n所需技能：創造 10等級以上', 'skill_level': 20, 'skill_effect': '消耗40 MP、100乙太\n每把乙太之劍可存在40秒，並造成240%傷害2次\n最多可對4把乙太之劍下達命令，當下達命令的數量超過可命令數量上限時，剩餘持續時間最短的乙太之劍將消失\n攻擊命中時，有15%機率生成乙太結晶\n冷卻時間：0.50秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMD', 'skill_effect_next': None}, {'skill_name': '回歸', 'skill_description': '[等級上限 : 20]\r\n讓下達追蹤命令的所有乙太之劍返回。乙太之劍將直線返回施展技能的地點，並在攻擊路徑上的敵人後，停留在移動位置上一段時間。使用瞄準模式後，乙太之劍就會揮向刻有死亡標記的敵人。但僅限在追蹤攻擊範圍內生效。須有因追蹤而正在追蹤敵人的乙太之劍才能使用。\n回歸發動時，乙太之劍的持續時間將不消耗。回歸攻擊即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害且不受冷卻時間重置效果影響。\n瞄準模式開關：右擊滑鼠\r\n所需技能：追蹤 5等級以上', 'skill_level': 20, 'skill_effect': '消耗50 MP、最多對10名敵人造成4次的260%傷害\n攻擊命中時，以40%機率生成乙太結晶\n冷卻時間12秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMC', 'skill_effect_next': None}, {'skill_name': '劍域', 'skill_description': '[等級上限 : 20]\r\n設置屬於自己的領域，並創造出無數把劍。即使攻擊，反射攻擊狀態的敵人，也不會遭受傷害。', 'skill_level': 20, 'skill_effect': '消耗120 MP，生成特殊領域7秒，該領域將定期對最多8名敵人造成100%傷害4次\n持續時間結束時，幻劍將反轉，並對最多12名敵人追加造成550%傷害12次\n冷卻時間：30秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMB', 'skill_effect_next': None}, {'skill_name': '高潔精神', 'skill_description': '[等級上限 : 10]\r\n為了同伴而發揮犧牲自我的高尚精神。在自己周圍生成的領域內，若有包含自己在內的隊員遭受傷害時，代為承受部分傷害並依其傷害量形成護盾。\n不適用Buff持續時間增加效果，再次使用技能時將立即取消技能。', 'skill_level': 10, 'skill_effect': '消耗200 MP，生成特殊領域20秒\n代替領域內的隊員承受30%所受傷害，並生成等同80%該傷害量的護盾\n當代替承受的傷害量高於自己剩餘的HP時，則不代替承受\n冷卻時間：120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBMF', 'skill_effect_next': None}, {'skill_name': '羽翼', 'skill_description': '[等級上限 : 4]\r\n如羽毛般輕盈地移動到後方，於空中進行短暫的全體攻擊。\n使用踐踏以外的觸發技能時也可移動。', 'skill_level': 4, 'skill_effect': '消耗46 MP、30乙太\n朝後方移動一定距離\n冷卻時間：8秒\n[被動效果：增加5移動速度、10跳躍力、10最大移動速度]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGPBME', 'skill_effect_next': None}, {'skill_name': '上進', 'skill_description': '[等級上限 : 20]\r\n以無限的進取心讓進度幅度大躍進', 'skill_level': 20, 'skill_effect': '增加攻擊力30、最終傷害17%、爆擊機率20%\n碎片的傷害增加10%p\n創造的傷害增加240%p\n穿刺的傷害增加100%p\n魔劍共鳴的傷害增加115%p', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGOBMG', 'skill_effect_next': None}, {'skill_name': '耐性', 'skill_description': '[等級上限 : 10]\r\n培養耐性以面對各種危機。另外，永久增加無視怪物防禦率。', 'skill_level': 10, 'skill_effect': '格擋機率增加40%、最大HP增加10%、狀態異常抗性增加30、所有屬性抗性增加30%、無視怪物防禦率增加10%\n被攻擊時傷害減少20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKGOBMH', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[{'skill_name': '高級乙太', 'skill_description': '[等級上限 : 1]\\r\\n可對乙太進行更上一層的煉製', 'skill_level': 1, 'skill_effect': '最多可獲得400乙太\\n以創造生成，以及以追蹤命令的乙太之劍最大數量增加為6把', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBNC', 'skill_effect_next': None}, {'skill_name': '切割', 'skill_description': '[等級上限 : 30]\\r\\n[觸發技能] 形成巨劍截斷前方的敵人。', 'skill_level': 30, 'skill_effect': '消耗MP40，最多對7名敵人以375%傷害攻擊6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMA', 'skill_effect_next': None}, {'skill_name': '綻放', 'skill_description': '[等級上限 : 30]\\r\\n讓下達追蹤命令的所有乙太之劍旋轉並且引爆魔力。必須有下達追蹤命令正在追擊敵人的乙太之劍才可使用。\\n進行爆裂時，乙太之劍的持續時間不會流失，且無法引爆受到回歸指令而返回的乙太之劍。\\n即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害，不受冷卻時間重置效果影響。\\r\\n所需技能：追蹤 20等級以上', 'skill_level': 30, 'skill_effect': '消耗80 MP，每把乙太之劍將以對最多8名敵人造成650%傷害8次\\n當單一敵人被複數綻放命中時，綻放對該敵人的最終傷害減少25%\\n攻擊命中時，有50%機率生成乙太結晶\\n冷卻時間：20秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMD', 'skill_effect_next': None}, {'skill_name': '死亡標記', 'skill_description': '[等級上限 : 20]\\r\\n以詛咒之劍對敵人烙下死亡標記，藉此削弱其力量，並使其成為乙太之劍、碎片和魔力爆裂的目標。\\n若當前有被烙下死亡標記的敵人，欲再次使用技能或對其他敵人烙下死亡標記時，原先存在的死亡標記將消失。\\n在所有範圍內的敵人中，死亡標記將優先攻擊最大HP最高的敵人。\\r\\n所需技能：追蹤 20等級以上', 'skill_level': 20, 'skill_effect': '消耗MP150，對最多1名敵人造成220%傷害10次\\n當敵人身上有死亡標記時，追加無視其10%防禦率\\n若有敵人位於碎片/魔力爆裂/以追蹤下達命令的乙太之劍/以無限創造的乙太之劍的攻擊範圍內，並且身上帶有死亡標記時，將集中攻擊該名敵人', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMB', 'skill_effect_next': None}, {'skill_name': '護堤', 'skill_description': '[等級上限 : 20]\\r\\n讓乙太之劍在身體周圍快速旋轉，抵擋敵人的攻擊減少傷害。不受到冷卻時間初始化的效果的影響。\\n護堤施展期間不會被賦予致命性的狀態異常，若在施展護堤當下遭受攻擊，攻擊效果將起不了作用，之後會更加減少攻擊的傷害。使用除了踐踏以外的觸發技能時也能使用。', 'skill_level': 20, 'skill_effect': '消耗MP150，最多可長壓8秒。在長壓過程中，依最大HP的一定比例，減少40%包含造成傷害的攻擊在內的所受傷害\\n施放後 1秒內無敵，且若立即受到敵人攻擊，之後持續期間傷害減少量提升至55%。\\n技能結束時，每剩餘1秒長壓時間，冷卻時間減少3.5秒\\n冷卻時間：60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBME', 'skill_effect_next': None}, {'skill_name': '踐踏', 'skill_description': '[等級上限 : 20]\\r\\n[觸發技能] 讓魔力纏繞全身後急速下降。', 'skill_level': 20, 'skill_effect': '消耗MP 45，最多對6名敵方以550%的傷害攻擊6次\\n冷卻時間1.50秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMC', 'skill_effect_next': None}, {'skill_name': '雷普的勇士', 'skill_description': '[等級上限 : 30]\\r\\n因雷普的潛在力量，自己的所有能力值增加一定比例。使用技能時，將生成雷普的紋樣。', 'skill_level': 30, 'skill_effect': '消耗70MP，生成雷普的紋樣\\n[被動效果：直接投入AP的所有能力值增加15%]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMF', 'skill_effect_next': None}, {'skill_name': '雷普勇士的意志', 'skill_description': '[等級上限 : 5]\\r\\n集中精神，以解除狀態異常。使用後，在3秒內對狀態異常免疫。但不適用於部分狀態異常效果，且不適用於戰鬥命令。\\n即使在使用其他技能時，也可使用雷普勇士的意志。', 'skill_level': 5, 'skill_effect': '消耗MP 30，冷卻時間300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMG', 'skill_effect_next': None}, {'skill_name': '專家', 'skill_description': '[等級上限 : 30]\\r\\n增加調節器的熟練度、攻擊力、傷害。\\r\\n所需技能：精通 10等級以上', 'skill_level': 30, 'skill_effect': '增加調節器熟練度70%、30攻擊力、20%傷害', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBMH', 'skill_effect_next': None}, {'skill_name': '完美', 'skill_description': '[等級上限 : 30]\\r\\n透過修煉，讓技能的完成度趨於完美。', 'skill_level': 30, 'skill_effect': '碎片的傷害增加10%p\\n創造的傷害增加270%p\\n穿刺的傷害增加122%p \\n魔劍共鳴的傷害增加134%p\\n追蹤的傷害增加120%p\\n回歸的傷害增加300%p\\n劍域的傷害增加300%p', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBMI', 'skill_effect_next': None}, {'skill_name': '拆毀', 'skill_description': '[等級上限 : 20]\\r\\n學習能破壞敵人防禦的強大攻擊。', 'skill_level': 20, 'skill_effect': '最終傷害增加30%、無視防禦率增加20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBMJ', 'skill_effect_next': None}, {'skill_name': '登峰造極', 'skill_description': '[等級上限 : 20]\\r\\n透過持續不斷的戰鬥達到高手的境界。', 'skill_level': 20, 'skill_effect': '增加30攻擊力、13%傷害、20%爆擊機率、15%最大HP', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBNA', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '高級乙太', 'skill_description': '[等級上限 : 1]\r\n可對乙太進行更上一層的煉製', 'skill_level': 1, 'skill_effect': '最多可獲得400乙太\n以創造生成，以及以追蹤命令的乙太之劍最大數量增加為6把', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBNC', 'skill_effect_next': None}, {'skill_name': '切割', 'skill_description': '[等級上限 : 30]\r\n[觸發技能] 形成巨劍截斷前方的敵人。', 'skill_level': 30, 'skill_effect': '消耗MP40，最多對7名敵人以375%傷害攻擊6次', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMA', 'skill_effect_next': None}, {'skill_name': '綻放', 'skill_description': '[等級上限 : 30]\r\n讓下達追蹤命令的所有乙太之劍旋轉並且引爆魔力。必須有下達追蹤命令正在追擊敵人的乙太之劍才可使用。\n進行爆裂時，乙太之劍的持續時間不會流失，且無法引爆受到回歸指令而返回的乙太之劍。\n即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害，不受冷卻時間重置效果影響。\r\n所需技能：追蹤 20等級以上', 'skill_level': 30, 'skill_effect': '消耗80 MP，每把乙太之劍將以對最多8名敵人造成650%傷害8次\n當單一敵人被複數綻放命中時，綻放對該敵人的最終傷害減少25%\n攻擊命中時，有50%機率生成乙太結晶\n冷卻時間：20秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMD', 'skill_effect_next': None}, {'skill_name': '死亡標記', 'skill_description': '[等級上限 : 20]\r\n以詛咒之劍對敵人烙下死亡標記，藉此削弱其力量，並使其成為乙太之劍、碎片和魔力爆裂的目標。\n若當前有被烙下死亡標記的敵人，欲再次使用技能或對其他敵人烙下死亡標記時，原先存在的死亡標記將消失。\n在所有範圍內的敵人中，死亡標記將優先攻擊最大HP最高的敵人。\r\n所需技能：追蹤 20等級以上', 'skill_level': 20, 'skill_effect': '消耗MP150，對最多1名敵人造成220%傷害10次\n當敵人身上有死亡標記時，追加無視其10%防禦率\n若有敵人位於碎片/魔力爆裂/以追蹤下達命令的乙太之劍/以無限創造的乙太之劍的攻擊範圍內，並且身上帶有死亡標記時，將集中攻擊該名敵人', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMB', 'skill_effect_next': None}, {'skill_name': '護堤', 'skill_description': '[等級上限 : 20]\r\n讓乙太之劍在身體周圍快速旋轉，抵擋敵人的攻擊減少傷害。不受到冷卻時間初始化的效果的影響。\n護堤施展期間不會被賦予致命性的狀態異常，若在施展護堤當下遭受攻擊，攻擊效果將起不了作用，之後會更加減少攻擊的傷害。使用除了踐踏以外的觸發技能時也能使用。', 'skill_level': 20, 'skill_effect': '消耗MP150，最多可長壓8秒。在長壓過程中，依最大HP的一定比例，減少40%包含造成傷害的攻擊在內的所受傷害\n施放後 1秒內無敵，且若立即受到敵人攻擊，之後持續期間傷害減少量提升至55%。\n技能結束時，每剩餘1秒長壓時間，冷卻時間減少3.5秒\n冷卻時間：60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBME', 'skill_effect_next': None}, {'skill_name': '踐踏', 'skill_description': '[等級上限 : 20]\r\n[觸發技能] 讓魔力纏繞全身後急速下降。', 'skill_level': 20, 'skill_effect': '消耗MP 45，最多對6名敵方以550%的傷害攻擊6次\n冷卻時間1.50秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMC', 'skill_effect_next': None}, {'skill_name': '雷普的勇士', 'skill_description': '[等級上限 : 30]\r\n因雷普的潛在力量，自己的所有能力值增加一定比例。使用技能時，將生成雷普的紋樣。', 'skill_level': 30, 'skill_effect': '消耗70MP，生成雷普的紋樣\n[被動效果：直接投入AP的所有能力值增加15%]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMF', 'skill_effect_next': None}, {'skill_name': '雷普勇士的意志', 'skill_description': '[等級上限 : 5]\r\n集中精神，以解除狀態異常。使用後，在3秒內對狀態異常免疫。但不適用於部分狀態異常效果，且不適用於戰鬥命令。\n即使在使用其他技能時，也可使用雷普勇士的意志。', 'skill_level': 5, 'skill_effect': '消耗MP 30，冷卻時間300秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBMG', 'skill_effect_next': None}, {'skill_name': '專家', 'skill_description': '[等級上限 : 30]\r\n增加調節器的熟練度、攻擊力、傷害。\r\n所需技能：精通 10等級以上', 'skill_level': 30, 'skill_effect': '增加調節器熟練度70%、30攻擊力、20%傷害', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBMH', 'skill_effect_next': None}, {'skill_name': '完美', 'skill_description': '[等級上限 : 30]\r\n透過修煉，讓技能的完成度趨於完美。', 'skill_level': 30, 'skill_effect': '碎片的傷害增加10%p\n創造的傷害增加270%p\n穿刺的傷害增加122%p \n魔劍共鳴的傷害增加134%p\n追蹤的傷害增加120%p\n回歸的傷害增加300%p\n劍域的傷害增加300%p', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBMI', 'skill_effect_next': None}, {'skill_name': '拆毀', 'skill_description': '[等級上限 : 20]\r\n學習能破壞敵人防禦的強大攻擊。', 'skill_level': 20, 'skill_effect': '最終傷害增加30%、無視防禦率增加20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBMJ', 'skill_effect_next': None}, {'skill_name': '登峰造極', 'skill_description': '[等級上限 : 20]\r\n透過持續不斷的戰鬥達到高手的境界。', 'skill_level': 20, 'skill_effect': '增加30攻擊力、13%傷害、20%爆擊機率、15%最大HP', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBNA', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[{'skill_name': '連接繩索', 'skill_description': '[等級上限 : 30]\\r\\n將鐵鍊拋向天空，快速移動。', 'skill_level': 19, 'skill_effect': '上升途中若再次按技能鍵，即可取消\\n冷卻時間3秒\\n[被動效果：增加所有能力19]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMA', 'skill_effect_next': '上升途中若再次按技能鍵，即可取消\\n冷卻時間3秒\\n[被動效果：增加所有能力20]'}, {'skill_name': '實用的時空門', 'skill_description': '[等級上限 : 30]\\r\\n形成可通往最近村莊的傳送點。門消失之前可以多次進出，在傳送點上按 ↑ 鍵移動。', 'skill_level': 10, 'skill_effect': '消耗100 HP，維持傳送點50秒\\n冷卻時間為130秒\\n[被動效果：全屬性增加2]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMB', 'skill_effect_next': '消耗100 HP，維持傳送點52秒\\n冷卻時間為130秒\\n[被動效果：全屬性增加3]'}, {'skill_name': '實用的會心之眼', 'skill_description': '[等級上限 : 30]\\r\\n賦予自己能找出敵人的弱點造成致命傷的能力。不能跟會心之眼重複使用。', 'skill_level': 25, 'skill_effect': '消耗HP 100，在255秒內爆擊機率10%、爆擊傷害8%增加\\n冷卻時間 180秒\\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMC', 'skill_effect_next': '消耗HP 100，在258秒內爆擊機率10%、爆擊傷害8%增加\\n冷卻時間 180秒\\n[被動效果：全屬性 6增加]'}, {'skill_name': '實用的神聖之火', 'skill_description': '[等級上限 : 30]\\r\\n最大HP與最大MP的量增加。不會與神聖之火重複使用。', 'skill_level': 21, 'skill_effect': '消耗HP 100，在243秒內最大HP40%、最大MP40%增加\\n冷卻時間 180秒\\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMD', 'skill_effect_next': '消耗HP 100，在246秒內最大HP40%、最大MP40%增加\\n冷卻時間 180秒\\n[被動效果：全屬性 5增加]'}, {'skill_name': '實用的戰鬥命令', 'skill_description': '[等級上限 : 30]\\r\\n一定時間內提升自身的所有技能等級。限於4轉技能可以增加到最大等級以上，其他技能只能提高到最大等級為止。\\n部分例外的特別技能和初心者技能、戰鬥命令、實用的戰鬥命令、超技能、5轉、6轉技能的等級是無法提高技能等級。\\n無法與戰鬥命令重複使用。', 'skill_level': 22, 'skill_effect': '消耗HP 100，在246秒內所有技能等級+1\\n冷卻時間 180秒\\n[被動效果：狀態異常抗性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBME', 'skill_effect_next': '消耗HP 100，在249秒內所有技能等級+1\\n冷卻時間 180秒\\n[被動效果：狀態異常抗性 5增加]'}, {'skill_name': '實用的進階祝福', 'skill_description': '[等級上限 : 30]\\r\\n增加攻擊力、魔力、防禦力、最大HP、最大MP。\\n祝福、進階祝福、實用的進階祝福中，僅套用較高數值的效果。', 'skill_level': 15, 'skill_effect': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\\n[被動效果：全屬性增加3]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMF', 'skill_effect_next': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\\n[被動效果：全屬性增加4]'}, {'skill_name': '實用的最終極速', 'skill_description': '[等級上限 : 30]\\r\\n使自己的攻擊速度額外增加1階段。最終極速和實用的最終極速中，僅套用較高數值的效果。', 'skill_level': 22, 'skill_effect': '攻擊速度增加1階段\\n[被動效果：全屬性增加5]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMG', 'skill_effect_next': '攻擊速度增加1階段\\n[被動效果：全屬性增加5]'}, {'skill_name': '瞬移', 'skill_description': '[等級上限 : 30]\\r\\n瞬間移動到地圖上隨機的位置。在空中按壓按鍵時，會在一定時間內漂浮且慢速移動來代替瞬間移動。', 'skill_level': 22, 'skill_effect': '消耗HP 100\\n瞬間移動至地圖上的隨機位置\\n在空中長壓時可漂浮最多4.5秒\\n冷卻時間 20秒\\n[被動效果：攻擊力、魔力 22增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMH', 'skill_effect_next': '消耗HP 100\\n瞬間移動至地圖上的隨機位置\\n在空中長壓時可漂浮最多4.5秒\\n冷卻時間 20秒\\n[被動效果：攻擊力、魔力 23增加]'}, {'skill_name': '艾爾達斯的新星', 'skill_description': '[等級上限 : 30]\\r\\n收集自己周圍的艾爾達斯後朝敵人引爆攻擊。被攻擊的敵人體內艾爾達紊亂，陷入無法行動狀態。\\n艾爾達新星可在其他技能施放中使用，並可對攻擊無視與攻擊反射狀態的敵人造成傷害。', 'skill_level': 30, 'skill_effect': '消耗100 HP，對最多10名的敵人以330%的傷害攻擊5次，並進入無法行動狀態10秒\\n依照利用艾爾達斯的超新星對敵人造成的傷害而增加無法行動的持續時間，最多增加100%\\n冷卻時間 100秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMI', 'skill_effect_next': None}, {'skill_name': '艾爾達斯的意志', 'skill_description': '[等級上限 : 30]\\r\\n集中精神，以解除狀態異常。使用後，在3秒內對狀態異常免疫。但部分異常狀態效果不適用。\\n艾爾達斯的意志在使用其他技能時仍可使用。', 'skill_level': 16, 'skill_effect': '消耗100 HP，冷卻時間400秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMJ', 'skill_effect_next': '消耗100 HP，冷卻時間395秒'}, {'skill_name': '實用的祈禱', 'skill_description': '[等級上限 : 30]\\r\\n一定時間內狩獵怪物時，可獲得更多的經驗值和道具。不能跟神聖祈禱重複使用。', 'skill_level': 19, 'skill_effect': '消耗HP 100，237秒間獲得經驗值增加29%，掉寶率增加20%\\n冷卻時間 180秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBOA', 'skill_effect_next': '消耗HP 100，240秒間獲得經驗值增加30%，掉寶率增加20%\\n冷卻時間 180秒'}, {'skill_name': '艾爾達斯的降臨', 'skill_description': '[等級上限 : 30]\\r\\n釋放濃縮的艾爾達攻擊周圍敵人。\\n與方向鍵下同時使用時可召喚純淨艾爾達匯聚的物件艾爾達噴泉。\\n使用自訂指令時可不輸入方向鍵僅以技能鍵召喚艾爾達噴泉。\\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影侍從、祝雷、藍血、虛擬投影時，攻擊次數增加效果將改為相同效果的最終傷害增加。\\n指令開關：滑鼠右鍵', 'skill_level': 18, 'skill_effect': '消耗HP100\\n艾爾達斯降臨\\n最多向15名敵人以720%傷害攻擊6次，攻擊後吸收艾爾達斯，每個攻擊的敵人皆減少艾爾達斯降臨的冷卻時間2秒\\n冷卻時間40秒\\n艾爾達斯噴枯n60秒間召喚物體，每當物體在被召喚的地圖上消滅敵人時，從敵人那裡釋放的艾爾達斯會凝聚到物體周圍\\n消滅12名以上時，凝聚的艾爾達斯會釋出並最多向10名敵人以720%的傷害攻擊4次\\n冷卻時間60秒\\n艾爾達斯降臨和艾爾達斯噴泉的冷卻時間是共用的', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPG', 'skill_effect_next': '消耗HP100\\n艾爾達斯降臨\\n最多向15名敵人以735%傷害攻擊6次，攻擊後吸收艾爾達斯，每個攻擊的敵人皆減少艾爾達斯降臨的冷卻時間2秒\\n冷卻時間40秒\\n艾爾達斯噴枯n60秒間召喚物體，每當物體在被召喚的地圖上消滅敵人時，從敵人那裡釋放的艾爾達斯會凝聚到物體周圍\\n消滅12名以上時，凝聚的艾爾達斯會釋出並最多向10名敵人以735%的傷害攻擊4次\\n冷卻時間60秒\\n艾爾達斯降臨和艾爾達斯噴泉的冷卻時間是共用的'}, {'skill_name': '魔法迴路效能全開', 'skill_description': '[等級上限 : 30]\\r\\n魔力翅膀張開到最大將魔法迴路啟動到極限。', 'skill_level': 30, 'skill_effect': '消耗1000 MP，在60秒內，傷害增加45%\\n使用攻擊技能時，每4秒額外消耗150MP，並發動魔力暴風最多對6名敵人造成1100%傷害攻擊3次\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPH', 'skill_effect_next': None}, {'skill_name': '蜘蛛之鏡', 'skill_description': '[等級上限 : 30]\\r\\n利用威爾的艾爾達斯來崩壞空間，並把鏡面世界和現實世界連接後，把鏡面裡的蜘蛛具現在現實空間中。鏡面的蜘蛛攻擊處於反射狀態的敵人時，也不會使自己受傷。', 'skill_level': 1, 'skill_effect': '消耗HP 100\\n空間崩獺G以468%的傷害攻擊最多15名敵人15次後，召喚鏡中的蜘蛛\\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以182%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\\n冷卻時間：250秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPJ', 'skill_effect_next': '消耗HP 100\\n空間崩獺G以486%的傷害攻擊最多15名敵人15次後，召喚鏡中的蜘蛛\\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以189%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\\n冷卻時間：250秒'}, {'skill_name': '格蘭蒂斯女神的祝福', 'skill_description': '[等級上限 : 30]\\r\\n依據不同種族展現相異樣貌的格蘭蒂斯女神，賜予與種族相符的祝福。受冷卻時間減少效果影響。', 'skill_level': 30, 'skill_effect': 'HP 100消耗，持續40秒\\n超新星：使用技能時55%機率不受冷卻時間影響，最多6次不受影響\\n傷害35%增加\\n每個龍能球能量階段使凱撒的傷害追加增加11%\\n雷普：將除武器外的裝備中，不使用屬性的攻擊力/魔力100%轉換為使用屬性。但不適用套裝效果，僅能轉換武器純攻擊力/魔力的150%為使用屬性\\n攻擊力與魔力增加100\\n阿尼瑪：傷害增加40%\\n虎影的符籍與卷軸道力補充量增加75%，菈菈在龍脈迴響觸發時最終傷害增幅為11%，蓮的梅花劍絕技、亡魂劍絕技、蒼龍破天劍的最終傷害增加15%\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBIG', 'skill_effect_next': None}, {'skill_name': '烈陽印記', 'skill_description': '[等級上限 : 30]\\r\\n利用米特拉的力量釋出太陽的熱氣後，具現出火焰的憤怒。火焰的紋樣即使對反射攻擊狀態的敵人進行攻擊也不會受到傷害。', 'skill_level': 2, 'skill_effect': '消耗HP 100\\n米特拉的火焰：以810%的傷害攻擊最多15名敵人12次後，召喚火焰的紋樣\\n火焰的紋樣：維持51秒，並每2.1秒以216%攻擊最多2名敵人6次，若僅攻擊1名敵人則以297%攻擊\\n冷卻時間：250秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBJJ', 'skill_effect_next': '消耗HP 100\\n米特拉的火焰：以840%的傷害攻擊最多15名敵人12次後，召喚火焰的紋樣\\n火焰的紋樣：維持51秒，並每2.1秒以224%攻擊最多2名敵人6次，若僅攻擊1名敵人則以308%攻擊\\n冷卻時間：250秒'}, {'skill_name': '實用的神聖之泉', 'skill_description': '[等級上限 : 30]\\r\\n召喚神聖的噴水池以神聖的力量恢復隊員的生命。不死狀態的隊員亦可使用，只要走到噴泉旁並點擊上方向鍵，即可恢復。\\n包括自己在內，地圖中僅限存在一個隊員使用過的神聖之泉或實用的神聖之泉。\\n當實用的神聖之泉在持續時間結束前消失時，將留下神聖之痕不可在有隊員的神聖之泉/實用的神聖之泉/神聖之痕的地圖中使用。\\n不適用冷卻時間初始化、恢復技能效率增加、召喚獸持續時間增加效果，並且無法在傳送點附近召喚。', 'skill_level': 19, 'skill_effect': '消耗100 HP，持續49秒。使用時將恢復20%HP，共可使用14次\\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\\n冷卻時間為71秒\\n[被動效果：全屬性增加4]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBFH', 'skill_effect_next': '消耗100 HP，持續50秒。使用時將恢復25%HP，共可使用15次\\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\\n冷卻時間為70秒\\n[被動效果：全屬性增加4]'}, {'skill_name': '碎片/奇蹟強化', 'skill_description': '[等級上限 : 60]\\r\\n強化碎片/奇蹟。\\n\\n20級：攻擊一般怪物時傷害10%增加\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '碎片/奇蹟的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAII', 'skill_effect_next': None}, {'skill_name': '行星強化', 'skill_description': '[等級上限 : 60]\\r\\n強化行星。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '行星的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIG', 'skill_effect_next': None}, {'skill_name': '閃擊強化', 'skill_description': '[等級上限 : 60]\\r\\n強化閃擊。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '閃擊的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIH', 'skill_effect_next': None}, {'skill_name': '刺擊強化', 'skill_description': '[等級上限 : 60]\\r\\n強化刺擊。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '刺擊的最終傷害增加300%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJA', 'skill_effect_next': None}, {'skill_name': '十字斬強化', 'skill_description': '[等級上限 : 60]\\r\\n強化十字斬。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '十字斬的最終傷害增加180%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJB', 'skill_effect_next': None}, {'skill_name': '穿刺強化', 'skill_description': '[等級上限 : 60]\\r\\n強化穿刺。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '穿刺的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJC', 'skill_effect_next': None}, {'skill_name': '魔劍共鳴強化', 'skill_description': '[等級上限 : 60]\\r\\n強化魔劍共鳴。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔劍共鳴的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJD', 'skill_effect_next': None}, {'skill_name': '魔力爆裂強化', 'skill_description': '[等級上限 : 60]\\r\\n強化魔力爆裂。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔力爆裂的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJE', 'skill_effect_next': None}, {'skill_name': '創造強化', 'skill_description': '[等級上限 : 60]\\r\\n強化創造。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '創造的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJF', 'skill_effect_next': None}, {'skill_name': '回歸強化', 'skill_description': '[等級上限 : 60]\\r\\n強化回歸。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率強化20%', 'skill_level': 60, 'skill_effect': '回歸的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJG', 'skill_effect_next': None}, {'skill_name': '劍域強化', 'skill_description': '[等級上限 : 60]\\r\\n強化劍域。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '劍域的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJH', 'skill_effect_next': None}, {'skill_name': '踐踏強化', 'skill_description': '[等級上限 : 60]\\r\\n強化踐踏。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '踐踏的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJI', 'skill_effect_next': None}, {'skill_name': '切割強化', 'skill_description': '[等級上限 : 60]\\r\\n強化切割。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '切割的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJJ', 'skill_effect_next': None}, {'skill_name': '追蹤強化', 'skill_description': '[等級上限 : 60]\\r\\n強化追蹤。\\n\\n20級：攻擊一般怪物時傷害10%增加\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '追蹤的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKA', 'skill_effect_next': None}, {'skill_name': '死亡標記強化', 'skill_description': '[等級上限 : 60]\\r\\n強化死亡標記。\\n\\n20級：攻擊一般怪物時傷害10%增加\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '死亡標記的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKB', 'skill_effect_next': None}, {'skill_name': '綻放強化', 'skill_description': '[等級上限 : 60]\\r\\n強化綻放。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '綻放的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKC', 'skill_effect_next': None}, {'skill_name': '狂風強化', 'skill_description': '[等級上限 : 60]\\r\\n強化狂風。\\n\\n20級：最大可攻擊對象+1\\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '狂風的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKD', 'skill_effect_next': None}, {'skill_name': '幻靈武具', 'skill_description': '[等級上限 : 30]\\r\\n將部分生命力賦予武器，發揮強大的力量。', 'skill_level': 30, 'skill_effect': '消耗100 HP，130秒內無視怪物防禦率 16%，最終傷害值增加6% 。\\n每5秒使用自己的攻擊技能時，發射鬥氣波動攻擊敵人，最多對10名敵人造成1100%傷害6次\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBMA', 'skill_effect_next': None}, {'skill_name': '鋼鐵之軀', 'skill_description': '[等級上限 : 30]\\r\\n肉體變成和鋼鐵一樣，不會受敵人的攻擊彈開。', 'skill_level': 30, 'skill_effect': '消耗100 HP，在18秒內，不會被任何攻擊擊退，並提升狀態異常抗性80\\n冷卻時間120秒\\n[被動效果：力量增加30、最大HP增加1500]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBKG', 'skill_effect_next': None}, {'skill_name': '毀滅', 'skill_description': '[等級上限 : 30]\\r\\n召喚古代滅亡之劍讓四周崩毀。\\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害。', 'skill_level': 30, 'skill_effect': '消耗MP1000，最多攻擊15名敵人\\n召喚後，發動以1012%傷害攻擊6次的攻擊12次\\n召喚後插上劍，發動以1485%傷害攻擊9次的攻擊8次\\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMF', 'skill_effect_next': None}, {'skill_name': '無限', 'skill_description': '[等級上限 : 30]\\r\\n創造一個空間，讓無數的乙太之劍生成。乙太之劍只會在阿戴爾附近追擊敵人，當劍和阿戴爾之間的距離變遠，劍會移動到阿戴爾附近追擊新敵人。\\n以無限指令創造出來的乙太之劍會進行回歸；不套用爆裂，只套用死亡標記。\\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害，只有在阿戴爾處於戰鬥狀態時才會追擊敵人。\\r\\n所需技能：死亡標記 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP1000，在進行施展及解除動作時無敵\\n存在20秒，創造18把乙太之劍，可以770%傷害攻擊2次\\n攻擊命中時以5%機率形成乙太結晶\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMI', 'skill_effect_next': None}, {'skill_name': '復原', 'skill_description': '[等級上限 : 30]\\r\\n暫時修復燒焦的魔力迴路，讓過去的魔力之翼復活。\\n復原的攻擊可無視打擊，並且可對反射攻勢狀態的敵人造成傷害，再次使用技能時會立刻消失。\\r\\n所需技能：高潔精神 10等級以上', 'skill_level': 30, 'skill_effect': '施放及施放後，每秒消耗最大MP的2%\\n20秒內，傷害增加45%、乙太獲得量增加80%、可聽從追蹤命令的乙太之劍增加2把。施展時，無論持有多少乙太之劍，立即命令2把乙太之劍\\n每隔一定時間展開魔力翅膀，最多對6名敵人造成1980%傷害攻擊3次，恢復包含自身在內的隊員最大HP的10.5%\\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMJ', 'skill_effect_next': None}, {'skill_name': '乙太風暴', 'skill_description': '[等級上限 : 30]\\r\\n讓下達追蹤命令的所有乙太之劍在自身周圍有如暴風般地移動。以追蹤追擊敵人的乙太之劍數量比例，在自身周圍產生幻影移動。暴風攻擊即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。再次使用技能時可立即結束。\\r\\n所需技能：回歸 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP500，14秒內每隔一段時間會最多向7名敵人以869%傷害自動攻擊2次\\n施展時下達命令的乙太之劍每超出1雙，攻擊次數增加2次\\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAPG', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '連接繩索', 'skill_description': '[等級上限 : 30]\r\n將鐵鍊拋向天空，快速移動。', 'skill_level': 19, 'skill_effect': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力19]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMA', 'skill_effect_next': '上升途中若再次按技能鍵，即可取消\n冷卻時間3秒\n[被動效果：增加所有能力20]'}, {'skill_name': '實用的時空門', 'skill_description': '[等級上限 : 30]\r\n形成可通往最近村莊的傳送點。門消失之前可以多次進出，在傳送點上按 ↑ 鍵移動。', 'skill_level': 10, 'skill_effect': '消耗100 HP，維持傳送點50秒\n冷卻時間為130秒\n[被動效果：全屬性增加2]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMB', 'skill_effect_next': '消耗100 HP，維持傳送點52秒\n冷卻時間為130秒\n[被動效果：全屬性增加3]'}, {'skill_name': '實用的會心之眼', 'skill_description': '[等級上限 : 30]\r\n賦予自己能找出敵人的弱點造成致命傷的能力。不能跟會心之眼重複使用。', 'skill_level': 25, 'skill_effect': '消耗HP 100，在255秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMC', 'skill_effect_next': '消耗HP 100，在258秒內爆擊機率10%、爆擊傷害8%增加\n冷卻時間 180秒\n[被動效果：全屬性 6增加]'}, {'skill_name': '實用的神聖之火', 'skill_description': '[等級上限 : 30]\r\n最大HP與最大MP的量增加。不會與神聖之火重複使用。', 'skill_level': 21, 'skill_effect': '消耗HP 100，在243秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMD', 'skill_effect_next': '消耗HP 100，在246秒內最大HP40%、最大MP40%增加\n冷卻時間 180秒\n[被動效果：全屬性 5增加]'}, {'skill_name': '實用的戰鬥命令', 'skill_description': '[等級上限 : 30]\r\n一定時間內提升自身的所有技能等級。限於4轉技能可以增加到最大等級以上，其他技能只能提高到最大等級為止。\n部分例外的特別技能和初心者技能、戰鬥命令、實用的戰鬥命令、超技能、5轉、6轉技能的等級是無法提高技能等級。\n無法與戰鬥命令重複使用。', 'skill_level': 22, 'skill_effect': '消耗HP 100，在246秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBME', 'skill_effect_next': '消耗HP 100，在249秒內所有技能等級+1\n冷卻時間 180秒\n[被動效果：狀態異常抗性 5增加]'}, {'skill_name': '實用的進階祝福', 'skill_description': '[等級上限 : 30]\r\n增加攻擊力、魔力、防禦力、最大HP、最大MP。\n祝福、進階祝福、實用的進階祝福中，僅套用較高數值的效果。', 'skill_level': 15, 'skill_effect': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加3]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMF', 'skill_effect_next': '增加20攻擊力、20魔力、425防禦力、475最大HP、475最大MP\n[被動效果：全屬性增加4]'}, {'skill_name': '實用的最終極速', 'skill_description': '[等級上限 : 30]\r\n使自己的攻擊速度額外增加1階段。最終極速和實用的最終極速中，僅套用較高數值的效果。', 'skill_level': 22, 'skill_effect': '攻擊速度增加1階段\n[被動效果：全屬性增加5]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHOBMG', 'skill_effect_next': '攻擊速度增加1階段\n[被動效果：全屬性增加5]'}, {'skill_name': '瞬移', 'skill_description': '[等級上限 : 30]\r\n瞬間移動到地圖上隨機的位置。在空中按壓按鍵時，會在一定時間內漂浮且慢速移動來代替瞬間移動。', 'skill_level': 22, 'skill_effect': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 22增加]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMH', 'skill_effect_next': '消耗HP 100\n瞬間移動至地圖上的隨機位置\n在空中長壓時可漂浮最多4.5秒\n冷卻時間 20秒\n[被動效果：攻擊力、魔力 23增加]'}, {'skill_name': '艾爾達斯的新星', 'skill_description': '[等級上限 : 30]\r\n收集自己周圍的艾爾達斯後朝敵人引爆攻擊。被攻擊的敵人體內艾爾達紊亂，陷入無法行動狀態。\n艾爾達新星可在其他技能施放中使用，並可對攻擊無視與攻擊反射狀態的敵人造成傷害。', 'skill_level': 30, 'skill_effect': '消耗100 HP，對最多10名的敵人以330%的傷害攻擊5次，並進入無法行動狀態10秒\n依照利用艾爾達斯的超新星對敵人造成的傷害而增加無法行動的持續時間，最多增加100%\n冷卻時間 100秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMI', 'skill_effect_next': None}, {'skill_name': '艾爾達斯的意志', 'skill_description': '[等級上限 : 30]\r\n集中精神，以解除狀態異常。使用後，在3秒內對狀態異常免疫。但部分異常狀態效果不適用。\n艾爾達斯的意志在使用其他技能時仍可使用。', 'skill_level': 16, 'skill_effect': '消耗100 HP，冷卻時間400秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBMJ', 'skill_effect_next': '消耗100 HP，冷卻時間395秒'}, {'skill_name': '實用的祈禱', 'skill_description': '[等級上限 : 30]\r\n一定時間內狩獵怪物時，可獲得更多的經驗值和道具。不能跟神聖祈禱重複使用。', 'skill_level': 19, 'skill_effect': '消耗HP 100，237秒間獲得經驗值增加29%，掉寶率增加20%\n冷卻時間 180秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBOA', 'skill_effect_next': '消耗HP 100，240秒間獲得經驗值增加30%，掉寶率增加20%\n冷卻時間 180秒'}, {'skill_name': '艾爾達斯的降臨', 'skill_description': '[等級上限 : 30]\r\n釋放濃縮的艾爾達攻擊周圍敵人。\n與方向鍵下同時使用時可召喚純淨艾爾達匯聚的物件艾爾達噴泉。\n使用自訂指令時可不輸入方向鍵僅以技能鍵召喚艾爾達噴泉。\n套用影分身、替身術、壓制砲擊、沉月、雙重力量、暗影侍從、祝雷、藍血、虛擬投影時，攻擊次數增加效果將改為相同效果的最終傷害增加。\n指令開關：滑鼠右鍵', 'skill_level': 18, 'skill_effect': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPG', 'skill_effect_next': '消耗HP 100\n艾爾達斯降臨\n最多朝15名敵人以0%的傷害攻擊0次，攻擊後吸收艾爾達，每攻擊一名敵人艾爾達斯降臨的再使用冷卻時間減少2秒\n冷卻時間40秒\n艾爾達斯噴?召喚物件持續60秒，每隔一定時間最多攻擊10名敵人，以0%的傷害攻擊0次\n重新使用技能可重新召喚物件\n冷卻時間 60秒\n艾爾達斯降臨與艾爾達斯噴泉共享再使用冷卻時間'}, {'skill_name': '魔法迴路效能全開', 'skill_description': '[等級上限 : 30]\r\n魔力翅膀張開到最大將魔法迴路啟動到極限。', 'skill_level': 30, 'skill_effect': '消耗1000 MP，在60秒內，傷害增加45%\n使用攻擊技能時，每4秒額外消耗150MP，並發動魔力暴風最多對6名敵人造成1100%傷害攻擊3次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPH', 'skill_effect_next': None}, {'skill_name': '蜘蛛之鏡', 'skill_description': '[等級上限 : 30]\r\n利用威爾的艾爾達斯來崩壞空間，並把鏡面世界和現實世界連接後，把鏡面裡的蜘蛛具現在現實空間中。鏡面的蜘蛛攻擊處於反射狀態的敵人時，也不會使自己受傷。', 'skill_level': 1, 'skill_effect': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBPJ', 'skill_effect_next': '消耗HP 100\n空間崩獺G以0%的傷害攻擊最多15名敵人0次後，召喚鏡中的蜘蛛\n鏡中的蜘蛛：持續50秒，並依一定時間進入攻擊狀態，在攻擊狀態中使用10次蜘蛛腳，以0%的傷害攻擊8次，若蜘蛛腳連續攻擊同一名敵人5次則立即結束攻擊狀態，攻擊狀態結束後再進入冷卻時間3秒\n冷卻時間：240秒'}, {'skill_name': '格蘭蒂斯女神的祝福', 'skill_description': '[等級上限 : 30]\r\n依據不同種族展現相異樣貌的格蘭蒂斯女神，賜予與種族相符的祝福。受冷卻時間減少效果影響。', 'skill_level': 30, 'skill_effect': 'HP 100消耗，持續40秒\n超新星：使用技能時55%機率不受冷卻時間影響，最多6次不受影響\n傷害35%增加\n每個龍能球能量階段使凱撒的傷害追加增加11%\n雷普：將除武器外的裝備中，不使用屬性的攻擊力/魔力100%轉換為使用屬性。但不適用套裝效果，僅能轉換武器純攻擊力/魔力的150%為使用屬性\n攻擊力與魔力增加100\n阿尼瑪：傷害增加40%\n虎影的符籍與卷軸道力補充量增加75%，菈菈在龍脈迴響觸發時最終傷害增幅為11%，蓮的梅花劍絕技、亡魂劍絕技、蒼龍破天劍的最終傷害增加15%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBIG', 'skill_effect_next': None}, {'skill_name': '烈陽印記', 'skill_description': '[等級上限 : 30]\r\n利用米特拉的力量釋出太陽的熱氣後，具現出火焰的憤怒。火焰的紋樣即使對反射攻擊狀態的敵人進行攻擊也不會受到傷害。', 'skill_level': 2, 'skill_effect': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBJJ', 'skill_effect_next': '消耗HP 100\n米特拉的火焰：以0%的傷害攻擊最多15名敵人0次後，召喚火焰的紋樣\n火焰的紋樣：維持51秒，並每2.1秒以0%攻擊最多2名敵人6次，若僅攻擊1名敵人則以0%攻擊\n冷卻時間：240秒'}, {'skill_name': '實用的神聖之泉', 'skill_description': '[等級上限 : 30]\r\n召喚神聖的噴泉，用神聖的力量恢復隊員的HP。不死狀態的隊員也可使用，靠近噴泉並按下向上方向鍵即可回復HP。\n包含自身在內的隊員所使用的神聖之泉及實用的神聖之泉，在地圖內只能存在一個。\n實用的神聖之泉在持續時間結束前消失時，會留下神聖之痕。在存在神聖之泉以及除自身外隊員的實用的神聖之泉及神聖之痕的地圖中無法使用。\n不受再使用冷卻時間重置、回復技能效率增加、增加召喚獸持續時間效果影響，且無法在傳送點附近召喚。', 'skill_level': 19, 'skill_effect': '消耗100 HP，持續49秒。使用時將恢復20%HP，共可使用14次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為71秒\n[被動效果：全屬性增加4]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHPBFH', 'skill_effect_next': '消耗100 HP，持續50秒。使用時將恢復25%HP，共可使用15次\n在持續時間結束前消失時，將生成神聖之痕直到剩餘的持續時間耗盡\n冷卻時間為70秒\n[被動效果：全屬性增加4]'}, {'skill_name': '碎片/奇蹟強化', 'skill_description': '[等級上限 : 60]\r\n強化碎片/奇蹟。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '碎片/奇蹟的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAII', 'skill_effect_next': None}, {'skill_name': '行星強化', 'skill_description': '[等級上限 : 60]\r\n強化行星。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '行星的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIG', 'skill_effect_next': None}, {'skill_name': '閃擊強化', 'skill_description': '[等級上限 : 60]\r\n強化閃擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '閃擊的最終傷害增加420%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAIH', 'skill_effect_next': None}, {'skill_name': '刺擊強化', 'skill_description': '[等級上限 : 60]\r\n強化刺擊。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '刺擊的最終傷害增加300%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJA', 'skill_effect_next': None}, {'skill_name': '十字斬強化', 'skill_description': '[等級上限 : 60]\r\n強化十字斬。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '十字斬的最終傷害增加180%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJB', 'skill_effect_next': None}, {'skill_name': '穿刺強化', 'skill_description': '[等級上限 : 60]\r\n強化穿刺。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '穿刺的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJC', 'skill_effect_next': None}, {'skill_name': '魔劍共鳴強化', 'skill_description': '[等級上限 : 60]\r\n強化魔劍共鳴。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔劍共鳴的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJD', 'skill_effect_next': None}, {'skill_name': '魔力爆裂強化', 'skill_description': '[等級上限 : 60]\r\n強化魔力爆裂。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '魔力爆裂的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJE', 'skill_effect_next': None}, {'skill_name': '創造強化', 'skill_description': '[等級上限 : 60]\r\n強化創造。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '創造的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJF', 'skill_effect_next': None}, {'skill_name': '回歸強化', 'skill_description': '[等級上限 : 60]\r\n強化回歸。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率強化20%', 'skill_level': 60, 'skill_effect': '回歸的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJG', 'skill_effect_next': None}, {'skill_name': '劍域強化', 'skill_description': '[等級上限 : 60]\r\n強化劍域。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '劍域的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJH', 'skill_effect_next': None}, {'skill_name': '踐踏強化', 'skill_description': '[等級上限 : 60]\r\n強化踐踏。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '踐踏的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJI', 'skill_effect_next': None}, {'skill_name': '切割強化', 'skill_description': '[等級上限 : 60]\r\n強化切割。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '切割的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAJJ', 'skill_effect_next': None}, {'skill_name': '追蹤強化', 'skill_description': '[等級上限 : 60]\r\n強化追蹤。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '追蹤的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKA', 'skill_effect_next': None}, {'skill_name': '死亡標記強化', 'skill_description': '[等級上限 : 60]\r\n強化死亡標記。\n\n20級：攻擊一般怪物時傷害10%增加\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '死亡標記的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKB', 'skill_effect_next': None}, {'skill_name': '綻放強化', 'skill_description': '[等級上限 : 60]\r\n強化綻放。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '綻放的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKC', 'skill_effect_next': None}, {'skill_name': '狂風強化', 'skill_description': '[等級上限 : 60]\r\n強化狂風。\n\n20級：最大可攻擊對象+1\n40級：無視怪物防禦率增加20%', 'skill_level': 60, 'skill_effect': '狂風的最終傷害增加120%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLHKAKD', 'skill_effect_next': None}, {'skill_name': '幻靈武具', 'skill_description': '[等級上限 : 30]\r\n將部分生命力賦予武器，發揮強大的力量。', 'skill_level': 30, 'skill_effect': '消耗100 HP，130秒內無視怪物防禦率 16%，最終傷害值增加6% 。\n每5秒使用自己的攻擊技能時，發射鬥氣波動攻擊敵人，最多對10名敵人造成1100%傷害6次\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBMA', 'skill_effect_next': None}, {'skill_name': '鋼鐵之軀', 'skill_description': '[等級上限 : 30]\r\n肉體變成和鋼鐵一樣，不會受敵人的攻擊彈開。', 'skill_level': 30, 'skill_effect': '消耗100 HP，在18秒內，不會被任何攻擊擊退，並提升狀態異常抗性80\n冷卻時間120秒\n[被動效果：力量增加30、最大HP增加1500]', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPBKG', 'skill_effect_next': None}, {'skill_name': '毀滅', 'skill_description': '[等級上限 : 30]\r\n召喚古代滅亡之劍讓四周崩毀。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害。', 'skill_level': 30, 'skill_effect': '消耗MP1000，最多攻擊15名敵人\n召喚後，發動以1012%傷害攻擊6次的攻擊12次\n召喚後插上劍，發動以1485%傷害攻擊9次的攻擊8次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMF', 'skill_effect_next': None}, {'skill_name': '無限', 'skill_description': '[等級上限 : 30]\r\n創造一個空間，讓無數的乙太之劍生成。乙太之劍只會在阿戴爾附近追擊敵人，當劍和阿戴爾之間的距離變遠，劍會移動到阿戴爾附近追擊新敵人。\n以無限指令創造出來的乙太之劍會進行回歸；不套用爆裂，只套用死亡標記。\n就算攻擊會反射攻勢狀態的敵人也不會受到傷害，只有在阿戴爾處於戰鬥狀態時才會追擊敵人。\r\n所需技能：死亡標記 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP1000，在進行施展及解除動作時無敵\n存在20秒，創造18把乙太之劍，可以770%傷害攻擊2次\n攻擊命中時以5%機率形成乙太結晶\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMI', 'skill_effect_next': None}, {'skill_name': '復原', 'skill_description': '[等級上限 : 30]\r\n暫時修復燒焦的魔力迴路，讓過去的魔力之翼復活。\n復原的攻擊可無視打擊，並且可對反射攻勢狀態的敵人造成傷害，再次使用技能時會立刻消失。\r\n所需技能：高潔精神 10等級以上', 'skill_level': 30, 'skill_effect': '施放及施放後，每秒消耗最大MP的2%\n20秒內，傷害增加45%、乙太獲得量增加80%、可聽從追蹤命令的乙太之劍增加2把。施展時，無論持有多少乙太之劍，立即命令2把乙太之劍\n每隔一定時間展開魔力翅膀，最多對6名敵人造成1980%傷害攻擊3次，恢復包含自身在內的隊員最大HP的10.5%\n冷卻時間120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAMJ', 'skill_effect_next': None}, {'skill_name': '乙太風暴', 'skill_description': '[等級上限 : 30]\r\n讓下達追蹤命令的所有乙太之劍在自身周圍有如暴風般地移動。以追蹤追擊敵人的乙太之劍數量比例，在自身周圍產生幻影移動。暴風攻擊即使攻擊處於反射攻擊狀態的敵人，也不會受到傷害。再次使用技能時可立即結束。\r\n所需技能：回歸 20等級以上', 'skill_level': 30, 'skill_effect': '消耗MP500，14秒內每隔一段時間會最多向7名敵人以869%傷害自動攻擊2次\n施展時下達命令的乙太之劍每超出1雙，攻擊次數增加2次\n冷卻時間60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KBPCLGPAPG', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[{'skill_name': '無限劍製', 'skill_description': '[等級上限 : 30]\\r\\n指揮無限的乙太之劍橫掃戰場。\\n\\n10級：無視怪物防禦率提升20%\\n20級：攻擊Boss怪物時傷害增加20%\\n30級：無視怪物防禦率增加30%、攻擊Boss怪物時傷害增加30%', 'skill_level': 1, 'skill_effect': '消耗MP1200、施展時無敵\\n召喚乙太之劍，最多鎖定15名敵人為目標，發動以703%的傷害攻擊10次的斬擊29次\\n最後操控乙太之劍，鎖定15名敵人，發動以703%的傷害攻擊14次的最終攻擊57次\\n冷卻時間為360秒 ', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKDPEMA', 'skill_effect_next': '消耗MP1200、施展時無敵\\n召喚乙太之劍，最多鎖定15名敵人為目標，發動以726%的傷害攻擊10次的斬擊29次\\n最後操控乙太之劍，鎖定15名敵人，發動以726%的傷害攻擊14次的最終攻擊57次\\n冷卻時間為360秒 '}]</t>
+          <t>[{'skill_name': '無限劍製', 'skill_description': '[等級上限 : 30]\r\n指揮無限的乙太之劍橫掃戰場。\n\n10級：無視怪物防禦率提升20%\n20級：攻擊Boss怪物時傷害增加20%\n30級：無視怪物防禦率增加30%、攻擊Boss怪物時傷害增加30%', 'skill_level': 1, 'skill_effect': '消耗MP1200、施展時無敵\n召喚乙太之劍，最多鎖定15名敵人為目標，發動以703%的傷害攻擊10次的斬擊29次\n最後操控乙太之劍，鎖定15名敵人，發動以703%的傷害攻擊14次的最終攻擊57次\n冷卻時間為360秒 ', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKDPEMA', 'skill_effect_next': '消耗MP1200、施展時無敵\n召喚乙太之劍，最多鎖定15名敵人為目標，發動以726%的傷害攻擊10次的斬擊29次\n最後操控乙太之劍，鎖定15名敵人，發動以726%的傷害攻擊14次的最終攻擊57次\n冷卻時間為360秒 '}]</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[{'skill_name': '觸發-強化', 'skill_description': '[等級上限 : 1]\\r\\n增加觸發技能的傷害。', 'skill_level': 1, 'skill_effect': '增加傷害20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPB', 'skill_effect_next': None}, {'skill_name': '觸發-無視防禦', 'skill_description': '[等級上限 : 1]\\r\\n增加觸發技能的無視防禦率數值。', 'skill_level': 0, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPC', 'skill_effect_next': '無視防禦率增加20%'}, {'skill_name': '觸發-BOSS殺手', 'skill_description': '[等級上限 : 1]\\r\\n攻擊觸發技能的BOSS怪物時增加傷害。', 'skill_level': 0, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPD', 'skill_effect_next': '攻擊BOSS怪時增加傷害20%'}, {'skill_name': '魔劍共鳴-額外治癒', 'skill_description': '[等級上限 : 1]\\r\\n當乙太結晶和魔劍共鳴後消失時可獲得乙太，此時使用穿刺不會消耗乙太。', 'skill_level': 1, 'skill_effect': '乙太結晶因魔劍共鳴消失時，獲得乙太20，使用穿刺時不消耗乙太', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPE', 'skill_effect_next': None}, {'skill_name': '劍域-持續', 'skill_description': '[等級上限 : 1]\\r\\n增加劍域的持續時間。', 'skill_level': 1, 'skill_effect': '持續時間增加4秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPF', 'skill_effect_next': None}, {'skill_name': '綻放-減少冷卻時間', 'skill_description': '[等級上限 : 1]\\r\\n減少綻放的冷卻時間。', 'skill_level': 1, 'skill_effect': '減少冷卻時間25%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPG', 'skill_effect_next': None}, {'skill_name': '特性培養-治癒強化', 'skill_description': '[等級上限 : 1]\\r\\n增加特性培養的恢復量。', 'skill_level': 0, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPH', 'skill_effect_next': '恢復比例增加3%，和既有恢復比例加總'}, {'skill_name': '高潔精神-護盾強化', 'skill_description': '[等級上限 : 1]\\r\\n持續高潔精神中，若存在盾護盾，會增加傷害。', 'skill_level': 0, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPI', 'skill_effect_next': '增加傷害15%'}, {'skill_name': '護堤-持續', 'skill_description': '[等級上限 : 1]\\r\\n增加護堤的最大長按時間。', 'skill_level': 1, 'skill_effect': '增加最大長按時間 2秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPJ', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '觸發-強化', 'skill_description': '[等級上限 : 1]\r\n增加觸發技能的傷害。', 'skill_level': 1, 'skill_effect': '增加傷害20%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPB', 'skill_effect_next': None}, {'skill_name': '觸發-無視防禦', 'skill_description': '[等級上限 : 1]\r\n增加觸發技能的無視防禦率數值。', 'skill_level': 0, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPC', 'skill_effect_next': '無視防禦率增加20%'}, {'skill_name': '觸發-BOSS殺手', 'skill_description': '[等級上限 : 1]\r\n攻擊觸發技能的BOSS怪物時增加傷害。', 'skill_level': 0, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPD', 'skill_effect_next': '攻擊BOSS怪時增加傷害20%'}, {'skill_name': '魔劍共鳴-額外治癒', 'skill_description': '[等級上限 : 1]\r\n當乙太結晶和魔劍共鳴後消失時可獲得乙太，此時使用穿刺不會消耗乙太。', 'skill_level': 1, 'skill_effect': '乙太結晶因魔劍共鳴消失時，獲得乙太20，使用穿刺時不消耗乙太', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPE', 'skill_effect_next': None}, {'skill_name': '劍域-持續', 'skill_description': '[等級上限 : 1]\r\n增加劍域的持續時間。', 'skill_level': 1, 'skill_effect': '持續時間增加4秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPF', 'skill_effect_next': None}, {'skill_name': '綻放-減少冷卻時間', 'skill_description': '[等級上限 : 1]\r\n減少綻放的冷卻時間。', 'skill_level': 1, 'skill_effect': '減少冷卻時間25%', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPG', 'skill_effect_next': None}, {'skill_name': '特性培養-治癒強化', 'skill_description': '[等級上限 : 1]\r\n增加特性培養的恢復量。', 'skill_level': 0, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPH', 'skill_effect_next': '恢復比例增加3%，和既有恢復比例加總'}, {'skill_name': '高潔精神-護盾強化', 'skill_description': '[等級上限 : 1]\r\n持續高潔精神中，若存在盾護盾，會增加傷害。', 'skill_level': 0, 'skill_effect': None, 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPI', 'skill_effect_next': '增加傷害15%'}, {'skill_name': '護堤-持續', 'skill_description': '[等級上限 : 1]\r\n增加護堤的最大長按時間。', 'skill_level': 1, 'skill_effect': '增加最大長按時間 2秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFOBPJ', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[{'skill_name': '狂風', 'skill_description': '[等級上限 : 1]\\r\\n插入無數把充滿魔力的劍封印敵人的行動。\\n敵人遭受攻擊時，會被迫抵抗無法行動的異常狀態90秒，這段時間內不會被賦予封鎖及其他技能所造成的無法行動異常狀態。\\r\\n所需技能：綻放 30等級以上', 'skill_level': 1, 'skill_effect': '消耗300MP，對最多6名敵人造成700%傷害12次\\n遭受攻擊的敵人將陷入無法行動狀態10秒\\n依狂風對敵人造成的傷害量，無法行動狀態的持續時間最多可增加100%\\n冷卻時間為120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBIA', 'skill_effect_next': None}, {'skill_name': '神之種族', 'skill_description': '[等級上限 : 1]\\r\\n借助雷普古代神之力獲得強大的力量。', 'skill_level': 1, 'skill_effect': '消耗100MP，60秒內，增加10%傷害\\n僅限雷普職業群的隊員適用效果\\n冷卻時間為120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBIC', 'skill_effect_next': None}, {'skill_name': '魔力爆裂', 'skill_description': '[等級上限 : 1]\\r\\n把魔力注入空中的小碎片，使其膨脹後引爆。\\n魔力會在爆裂的位置上凝聚形成乙太結晶，並且無視再生冷卻時間。\\r\\n所需技能：魔劍共鳴 10等級以上', 'skill_level': 1, 'skill_effect': '消耗250 MP，在最多7名敵人的位置上生成碎片\\n碎片生成和碎裂時，皆可對最多7名敵人造成2000%傷害6次\\n若實際可攻擊的敵人少於最多可攻擊的敵人數量時，將在任意位置生成最多7個碎片\\n若目標身上有死亡標記時，則碎片生成數量減少一半，並對最多7名敵人造成2500%傷害6次\\n碎片碎裂後，最多可生成7個乙太結晶\\n冷卻時間：60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBIB', 'skill_effect_next': None}]</t>
+          <t>[{'skill_name': '狂風', 'skill_description': '[等級上限 : 1]\r\n插入無數把充滿魔力的劍封印敵人的行動。\n敵人遭受攻擊時，會被迫抵抗無法行動的異常狀態90秒，這段時間內不會被賦予封鎖及其他技能所造成的無法行動異常狀態。\r\n所需技能：綻放 30等級以上', 'skill_level': 1, 'skill_effect': '消耗300MP，對最多6名敵人造成700%傷害12次\n遭受攻擊的敵人將陷入無法行動狀態10秒\n依狂風對敵人造成的傷害量，無法行動狀態的持續時間最多可增加100%\n冷卻時間為120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBIA', 'skill_effect_next': None}, {'skill_name': '神之種族', 'skill_description': '[等級上限 : 1]\r\n借助雷普古代神之力獲得強大的力量。', 'skill_level': 1, 'skill_effect': '消耗100MP，60秒內，增加10%傷害\n僅限雷普職業群的隊員適用效果\n冷卻時間為120秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBIC', 'skill_effect_next': None}, {'skill_name': '魔力爆裂', 'skill_description': '[等級上限 : 1]\r\n把魔力注入空中的小碎片，使其膨脹後引爆。\n魔力會在爆裂的位置上凝聚形成乙太結晶，並且無視再生冷卻時間。\r\n所需技能：魔劍共鳴 10等級以上', 'skill_level': 1, 'skill_effect': '消耗250 MP，在最多7名敵人的位置上生成碎片\n碎片生成和碎裂時，皆可對最多7名敵人造成2000%傷害6次\n若實際可攻擊的敵人少於最多可攻擊的敵人數量時，將在任意位置生成最多7個碎片\n若目標身上有死亡標記時，則碎片生成數量減少一半，並對最多7名敵人造成2500%傷害6次\n碎片碎裂後，最多可生成7個乙太結晶\n冷卻時間：60秒', 'skill_icon': 'https://open.api.nexon.com/static/maplestorytw/skill/icon/KEKDKFPBIB', 'skill_effect_next': None}]</t>
         </is>
       </c>
     </row>
